--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99973D2A-1F73-4F2C-8F3B-0FF86E73EDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6F349E-E30B-4DD3-A553-F4614DB65799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27990" windowHeight="14415" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="30" yWindow="1800" windowWidth="27990" windowHeight="14415" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="232">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -3496,18 +3496,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25F42A9-A13E-41B6-8ACC-85810A7C82E6}">
-  <dimension ref="A2:N206"/>
+  <dimension ref="A2:AC206"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3515,27 +3515,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -3576,8 +3576,48 @@
       <c r="N8" s="5" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC8" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -3588,7 +3628,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E9" s="5">
         <v>100</v>
@@ -3597,10 +3637,10 @@
         <v>2</v>
       </c>
       <c r="G9" s="5">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="H9" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="5">
         <v>0.5</v>
@@ -3615,13 +3655,55 @@
         <v>0</v>
       </c>
       <c r="M9" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>9</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="S9" s="5">
+        <v>30</v>
+      </c>
+      <c r="T9" s="5">
+        <v>100</v>
+      </c>
+      <c r="U9" s="5">
+        <v>2</v>
+      </c>
+      <c r="V9" s="5">
+        <v>2</v>
+      </c>
+      <c r="W9" s="5">
+        <v>1</v>
+      </c>
+      <c r="X9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -3632,7 +3714,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E10" s="5">
         <v>75</v>
@@ -3641,10 +3723,11 @@
         <v>1.5</v>
       </c>
       <c r="G10" s="5">
-        <v>1.8</v>
+        <f t="shared" ref="G10:G17" si="0">V10/3</f>
+        <v>0.6</v>
       </c>
       <c r="H10" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" s="5">
         <v>0.5</v>
@@ -3659,13 +3742,55 @@
         <v>0</v>
       </c>
       <c r="M10" s="5">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P10" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>4</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S10" s="5">
+        <v>60</v>
+      </c>
+      <c r="T10" s="5">
+        <v>75</v>
+      </c>
+      <c r="U10" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="V10" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="W10" s="5">
+        <v>2</v>
+      </c>
+      <c r="X10" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>4</v>
       </c>
@@ -3676,7 +3801,7 @@
         <v>135</v>
       </c>
       <c r="D11" s="5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5">
         <v>55</v>
@@ -3685,10 +3810,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="5">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="5">
         <v>0.5</v>
@@ -3703,13 +3828,55 @@
         <v>50</v>
       </c>
       <c r="M11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P11" s="5">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>8</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="S11" s="5">
+        <v>100</v>
+      </c>
+      <c r="T11" s="5">
+        <v>55</v>
+      </c>
+      <c r="U11" s="5">
+        <v>2</v>
+      </c>
+      <c r="V11" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="W11" s="5">
+        <v>2</v>
+      </c>
+      <c r="X11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>45</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>50</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>3</v>
       </c>
@@ -3720,7 +3887,7 @@
         <v>22</v>
       </c>
       <c r="D12" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E12" s="5">
         <v>60</v>
@@ -3729,10 +3896,11 @@
         <v>2</v>
       </c>
       <c r="G12" s="5">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>0.39999999999999997</v>
       </c>
       <c r="H12" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I12" s="5">
         <v>1</v>
@@ -3747,13 +3915,55 @@
         <v>50</v>
       </c>
       <c r="M12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P12" s="5">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>3</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S12" s="5">
+        <v>60</v>
+      </c>
+      <c r="T12" s="5">
+        <v>60</v>
+      </c>
+      <c r="U12" s="5">
+        <v>2</v>
+      </c>
+      <c r="V12" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="W12" s="5">
+        <v>10</v>
+      </c>
+      <c r="X12" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>50</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>4</v>
       </c>
@@ -3764,7 +3974,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="5">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E13" s="5">
         <v>50</v>
@@ -3773,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="5">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H13" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" s="5">
         <v>1</v>
@@ -3791,13 +4001,55 @@
         <v>0</v>
       </c>
       <c r="M13" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P13" s="5">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>8</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="S13" s="5">
+        <v>200</v>
+      </c>
+      <c r="T13" s="5">
+        <v>50</v>
+      </c>
+      <c r="U13" s="5">
+        <v>1</v>
+      </c>
+      <c r="V13" s="5">
+        <v>1</v>
+      </c>
+      <c r="W13" s="5">
+        <v>2</v>
+      </c>
+      <c r="X13" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>35</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>5</v>
       </c>
@@ -3808,7 +4060,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="5">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="E14" s="5">
         <v>40</v>
@@ -3817,10 +4069,10 @@
         <v>1.5</v>
       </c>
       <c r="G14" s="5">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="H14" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5">
         <v>1</v>
@@ -3835,13 +4087,55 @@
         <v>50</v>
       </c>
       <c r="M14" s="5">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P14" s="5">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>6</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S14" s="5">
+        <v>350</v>
+      </c>
+      <c r="T14" s="5">
+        <v>40</v>
+      </c>
+      <c r="U14" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="V14" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="W14" s="5">
+        <v>2</v>
+      </c>
+      <c r="X14" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>55</v>
+      </c>
+      <c r="AA14" s="5">
+        <v>50</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>6</v>
       </c>
@@ -3852,7 +4146,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="5">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="E15" s="5">
         <v>30</v>
@@ -3861,10 +4155,10 @@
         <v>1.3</v>
       </c>
       <c r="G15" s="5">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="H15" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I15" s="5">
         <v>2</v>
@@ -3879,13 +4173,55 @@
         <v>0</v>
       </c>
       <c r="M15" s="5">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P15" s="5">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>6</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S15" s="5">
+        <v>350</v>
+      </c>
+      <c r="T15" s="5">
+        <v>30</v>
+      </c>
+      <c r="U15" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="V15" s="5">
+        <v>2</v>
+      </c>
+      <c r="W15" s="5">
+        <v>10</v>
+      </c>
+      <c r="X15" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>75</v>
+      </c>
+      <c r="AA15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="AC15" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>7</v>
       </c>
@@ -3896,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="5">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E16" s="5">
         <v>25</v>
@@ -3905,10 +4241,10 @@
         <v>1.2</v>
       </c>
       <c r="G16" s="5">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I16" s="5">
         <v>2</v>
@@ -3923,13 +4259,55 @@
         <v>50</v>
       </c>
       <c r="M16" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P16" s="5">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>3</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S16" s="5">
+        <v>500</v>
+      </c>
+      <c r="T16" s="5">
+        <v>25</v>
+      </c>
+      <c r="U16" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="V16" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="W16" s="5">
+        <v>10</v>
+      </c>
+      <c r="X16" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="5">
+        <v>110</v>
+      </c>
+      <c r="AA16" s="5">
+        <v>50</v>
+      </c>
+      <c r="AB16" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>8</v>
       </c>
@@ -3940,7 +4318,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E17" s="5">
         <v>25</v>
@@ -3949,10 +4327,11 @@
         <v>1.2</v>
       </c>
       <c r="G17" s="5">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>0.79999999999999993</v>
       </c>
       <c r="H17" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I17" s="5">
         <v>2</v>
@@ -3967,68 +4346,110 @@
         <v>50</v>
       </c>
       <c r="M17" s="5">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="P17" s="5">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>1</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="T17" s="5">
+        <v>25</v>
+      </c>
+      <c r="U17" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="V17" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="W17" s="5">
+        <v>10</v>
+      </c>
+      <c r="X17" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="5">
+        <v>110</v>
+      </c>
+      <c r="AA17" s="5">
+        <v>50</v>
+      </c>
+      <c r="AB17" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>211</v>
       </c>
@@ -5034,7 +5455,7 @@
         <v>223</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" ref="L139:L140" si="0">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
+        <f t="shared" ref="L139:L140" si="1">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
         <v>調和は、犠牲に強く混沌に弱い。</v>
       </c>
     </row>
@@ -5055,7 +5476,7 @@
         <v>224</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>犠牲は、統制に強く調和に弱い。</v>
       </c>
     </row>

--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,15 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6F349E-E30B-4DD3-A553-F4614DB65799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAB93B6-7E79-48CF-87A5-EAD76F282955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="1800" windowWidth="27990" windowHeight="14415" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="435" yWindow="795" windowWidth="27990" windowHeight="14415" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId2"/>
-    <sheet name="system" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="224">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -2153,77 +2150,6 @@
   </si>
   <si>
     <t>tap to continue</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔女が出現するバトル</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シュツゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>wave終了</t>
-    <rPh sb="4" eb="6">
-      <t>シュウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3秒ウェイト</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BGMが1秒かけてフェードアウト</t>
-    <rPh sb="5" eb="6">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"C:\Users\user\.antigravity\game\files\SOUND\awaken_boss.mp3"が鳴り</t>
-    <rPh sb="62" eb="63">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>"C:\Users\user\.antigravity\game\files\EFFECT\warn001.png"が3秒かけて右から左へ流れてゆく</t>
-    <rPh sb="60" eb="61">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="64" eb="65">
-      <t>ミギ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>ヒダリ</t>
-    </rPh>
-    <rPh sb="69" eb="70">
-      <t>ナガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5秒ウェイト</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔女が降ってくる</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>フ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3634,10 +3560,11 @@
         <v>100</v>
       </c>
       <c r="F9" s="5">
-        <v>2</v>
+        <f>U9*3</f>
+        <v>6</v>
       </c>
       <c r="G9" s="5">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="5">
         <v>3</v>
@@ -3720,11 +3647,11 @@
         <v>75</v>
       </c>
       <c r="F10" s="5">
-        <v>1.5</v>
+        <f t="shared" ref="F10:F17" si="0">U10*3</f>
+        <v>4.5</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" ref="G10:G17" si="0">V10/3</f>
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H10" s="5">
         <v>4</v>
@@ -3807,10 +3734,11 @@
         <v>55</v>
       </c>
       <c r="F11" s="5">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G11" s="5">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="5">
         <v>4</v>
@@ -3893,11 +3821,11 @@
         <v>60</v>
       </c>
       <c r="F12" s="5">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.39999999999999997</v>
+        <v>0.3</v>
       </c>
       <c r="H12" s="5">
         <v>8</v>
@@ -3974,16 +3902,18 @@
         <v>15</v>
       </c>
       <c r="D13" s="5">
-        <v>100</v>
+        <f>S13/4</f>
+        <v>50</v>
       </c>
       <c r="E13" s="5">
         <v>50</v>
       </c>
       <c r="F13" s="5">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G13" s="5">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H13" s="5">
         <v>4</v>
@@ -4060,16 +3990,17 @@
         <v>17</v>
       </c>
       <c r="D14" s="5">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="E14" s="5">
         <v>40</v>
       </c>
       <c r="F14" s="5">
-        <v>1.5</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="G14" s="5">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="5">
         <v>4</v>
@@ -4146,16 +4077,17 @@
         <v>18</v>
       </c>
       <c r="D15" s="5">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="E15" s="5">
         <v>30</v>
       </c>
       <c r="F15" s="5">
-        <v>1.3</v>
+        <f t="shared" si="0"/>
+        <v>3.9000000000000004</v>
       </c>
       <c r="G15" s="5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H15" s="5">
         <v>8</v>
@@ -4232,16 +4164,18 @@
         <v>16</v>
       </c>
       <c r="D16" s="5">
-        <v>250</v>
+        <f t="shared" ref="D14:D17" si="1">S16/4</f>
+        <v>125</v>
       </c>
       <c r="E16" s="5">
         <v>25</v>
       </c>
       <c r="F16" s="5">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="G16" s="5">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="H16" s="5">
         <v>8</v>
@@ -4318,17 +4252,18 @@
         <v>23</v>
       </c>
       <c r="D17" s="5">
-        <v>500</v>
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="E17" s="5">
         <v>25</v>
       </c>
       <c r="F17" s="5">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.79999999999999993</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="5">
         <v>8</v>
@@ -4451,12 +4386,12 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.4">
@@ -4497,7 +4432,7 @@
         <v>26</v>
       </c>
       <c r="M38" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.4">
@@ -4535,7 +4470,7 @@
         <v>1.2</v>
       </c>
       <c r="M39" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.4">
@@ -4573,7 +4508,7 @@
         <v>1.6</v>
       </c>
       <c r="M40" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.4">
@@ -4611,7 +4546,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="M41" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.4">
@@ -4649,7 +4584,7 @@
         <v>3</v>
       </c>
       <c r="M42" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.4">
@@ -4687,7 +4622,7 @@
         <v>4</v>
       </c>
       <c r="M43" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.4">
@@ -4725,7 +4660,7 @@
         <v>5.4</v>
       </c>
       <c r="M44" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.4">
@@ -4806,7 +4741,7 @@
         <v>9</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D47" s="5">
         <v>23000</v>
@@ -4833,10 +4768,10 @@
         <v>10.8</v>
       </c>
       <c r="M47" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N47">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.4">
@@ -4847,7 +4782,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D48" s="5">
         <v>26000</v>
@@ -4875,7 +4810,7 @@
       </c>
       <c r="N48">
         <f>N47*180</f>
-        <v>18000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.4">
@@ -4886,7 +4821,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D49" s="5">
         <v>29000</v>
@@ -4921,7 +4856,7 @@
         <v>12</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D50" s="5">
         <v>32000</v>
@@ -4956,7 +4891,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D51" s="5">
         <v>35000</v>
@@ -4985,7 +4920,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C54" t="s">
         <v>54</v>
@@ -5018,7 +4953,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B57" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.4">
@@ -5037,7 +4972,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.4">
@@ -5056,32 +4991,32 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B65" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B66" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B67" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B68" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B69" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.4">
@@ -5092,12 +5027,12 @@
         <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B72" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C72" s="3"/>
     </row>
@@ -5109,12 +5044,12 @@
         <v>43</v>
       </c>
       <c r="C73" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B74" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.4">
@@ -5125,12 +5060,12 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B76" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
@@ -5141,12 +5076,12 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B78" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C78" s="4"/>
     </row>
@@ -5410,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L137" t="str">
         <f>K137&amp;"は、"&amp;K138&amp;"に強く"&amp;K141&amp;"に弱い。"</f>
@@ -5431,7 +5366,7 @@
         <v>255</v>
       </c>
       <c r="K138" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="L138" t="str">
         <f>K138&amp;"は、"&amp;K139&amp;"に強く"&amp;K137&amp;"に弱い。"</f>
@@ -5452,10 +5387,10 @@
         <v>107</v>
       </c>
       <c r="K139" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" ref="L139:L140" si="1">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
+        <f t="shared" ref="L139:L140" si="2">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
         <v>調和は、犠牲に強く混沌に弱い。</v>
       </c>
     </row>
@@ -5473,10 +5408,10 @@
         <v>191</v>
       </c>
       <c r="K140" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>犠牲は、統制に強く調和に弱い。</v>
       </c>
     </row>
@@ -5497,7 +5432,7 @@
         <v>225</v>
       </c>
       <c r="K141" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L141" t="str">
         <f>K141&amp;"は、"&amp;K137&amp;"に強く"&amp;K140&amp;"に弱い。"</f>
@@ -5863,12 +5798,12 @@
         <v>156</v>
       </c>
       <c r="B176" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B177" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
@@ -5933,675 +5868,46 @@
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE3AEFC-F7A2-4313-8B39-2F1AAADA39F3}">
-  <dimension ref="C2:O15"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="2" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <f>C2*C2</f>
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <f>C2/2*C2/2</f>
-        <v>0.25</v>
-      </c>
-      <c r="F2">
-        <f>C2*C2/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="G2">
-        <f>D2*150</f>
-        <v>150</v>
-      </c>
-      <c r="H2">
-        <f>E2*150</f>
-        <v>37.5</v>
-      </c>
-      <c r="I2">
-        <f>F2*150</f>
-        <v>75</v>
-      </c>
-      <c r="M2">
-        <f t="shared" ref="M2:M14" si="0">(C3^2)/4</f>
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <f>M2*150</f>
-        <v>150</v>
-      </c>
-      <c r="O2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D15" si="1">C3*C3</f>
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E15" si="2">C3/2*C3/2</f>
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F15" si="3">C3*C3/2</f>
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:I15" si="4">D3*150</f>
-        <v>600</v>
-      </c>
-      <c r="H3">
-        <f t="shared" si="4"/>
-        <v>150</v>
-      </c>
-      <c r="I3">
-        <f t="shared" si="4"/>
-        <v>300</v>
-      </c>
-      <c r="M3">
-        <f t="shared" si="0"/>
-        <v>2.25</v>
-      </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N14" si="5">M3*150</f>
-        <v>337.5</v>
-      </c>
-      <c r="O3">
-        <f>O2*2</f>
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="2"/>
-        <v>2.25</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="3"/>
-        <v>4.5</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="4"/>
-        <v>1350</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="4"/>
-        <v>337.5</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="4"/>
-        <v>675</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="5"/>
-        <v>600</v>
-      </c>
-      <c r="O4">
-        <f t="shared" ref="O4:O14" si="6">O3*2</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="4"/>
-        <v>2400</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="4"/>
-        <v>600</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="4"/>
-        <v>1200</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="0"/>
-        <v>6.25</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="5"/>
-        <v>937.5</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="6"/>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="2"/>
-        <v>6.25</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="3"/>
-        <v>12.5</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="4"/>
-        <v>3750</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="4"/>
-        <v>937.5</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="4"/>
-        <v>1875</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="5"/>
-        <v>1350</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="6"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="4"/>
-        <v>5400</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="4"/>
-        <v>1350</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="4"/>
-        <v>2700</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>12.25</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="5"/>
-        <v>1837.5</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="6"/>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="2"/>
-        <v>12.25</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="3"/>
-        <v>24.5</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="4"/>
-        <v>7350</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="4"/>
-        <v>1837.5</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="4"/>
-        <v>3675</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="5"/>
-        <v>2400</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="6"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="4"/>
-        <v>9600</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="4"/>
-        <v>2400</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="4"/>
-        <v>4800</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="0"/>
-        <v>20.25</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="5"/>
-        <v>3037.5</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="6"/>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="2"/>
-        <v>20.25</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="3"/>
-        <v>40.5</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="4"/>
-        <v>12150</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="4"/>
-        <v>3037.5</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="4"/>
-        <v>6075</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="5"/>
-        <v>3750</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="6"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="4"/>
-        <v>15000</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="4"/>
-        <v>3750</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="4"/>
-        <v>7500</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="0"/>
-        <v>30.25</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="5"/>
-        <v>4537.5</v>
-      </c>
-      <c r="O11">
-        <f t="shared" si="6"/>
-        <v>64000</v>
-      </c>
-    </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>121</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="2"/>
-        <v>30.25</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="3"/>
-        <v>60.5</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="4"/>
-        <v>18150</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="4"/>
-        <v>4537.5</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="4"/>
-        <v>9075</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="5"/>
-        <v>5400</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="6"/>
-        <v>128000</v>
-      </c>
-    </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="2"/>
-        <v>36</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="3"/>
-        <v>72</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="4"/>
-        <v>21600</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="4"/>
-        <v>5400</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="4"/>
-        <v>10800</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="0"/>
-        <v>42.25</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="5"/>
-        <v>6337.5</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="6"/>
-        <v>256000</v>
-      </c>
-    </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C14">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="1"/>
-        <v>169</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="2"/>
-        <v>42.25</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="3"/>
-        <v>84.5</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="4"/>
-        <v>25350</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="4"/>
-        <v>6337.5</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="4"/>
-        <v>12675</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="5"/>
-        <v>7350</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="6"/>
-        <v>512000</v>
-      </c>
-    </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C15">
-        <v>14</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="1"/>
-        <v>196</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="2"/>
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="3"/>
-        <v>98</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="4"/>
-        <v>29400</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="4"/>
-        <v>7350</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="4"/>
-        <v>14700</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8320DF29-F5ED-4686-9254-5FA5FD67331F}">
-  <dimension ref="B2:D8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="D7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DBA31B4-0606-451E-B576-99FB3D319585}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAB93B6-7E79-48CF-87A5-EAD76F282955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54123CEA-4E93-4E17-97D9-07A9D6FBD926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="795" windowWidth="27990" windowHeight="14415" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="525" yWindow="315" windowWidth="17355" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="225">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -3005,6 +3005,9 @@
   <si>
     <t>dps</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・雑魚敵夜限定強化更新　雑魚敵レベルが本来の+3になる　マップに設定のない場合、編成中キャラクターの一番レベルが高いキャラクター+3とする。　出現数が1.5倍になる　ウェーブ数が3になる　大きさが1.5倍になる　雑魚敵の攻撃射程が2倍になる　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　魔女出現時もレベルが同様に高レベルキャラクターの+5，HPは本来の2倍　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　　</t>
   </si>
 </sst>
 </file>
@@ -3422,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25F42A9-A13E-41B6-8ACC-85810A7C82E6}">
-  <dimension ref="A2:AC206"/>
+  <dimension ref="A2:AC208"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9" customWidth="1"/>
@@ -4164,7 +4167,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" ref="D14:D17" si="1">S16/4</f>
+        <f t="shared" ref="D16:D17" si="1">S16/4</f>
         <v>125</v>
       </c>
       <c r="E16" s="5">
@@ -5904,6 +5907,11 @@
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54123CEA-4E93-4E17-97D9-07A9D6FBD926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20162E1D-3031-4BCB-A997-D2DCF86D0814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="315" windowWidth="17355" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="2625" yWindow="405" windowWidth="20265" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
@@ -4392,17 +4392,17 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38" s="5" t="s">
         <v>14</v>
       </c>
@@ -4434,11 +4434,11 @@
       <c r="K38" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M38" t="s">
+      <c r="O38" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>9</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>35</v>
       </c>
       <c r="D39" s="5">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="E39" s="5">
         <v>40</v>
@@ -4472,11 +4472,14 @@
       <c r="K39" s="5">
         <v>1.2</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="5">
+        <v>3000</v>
+      </c>
+      <c r="O39" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>10</v>
       </c>
@@ -4487,7 +4490,7 @@
         <v>42</v>
       </c>
       <c r="D40" s="5">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="E40" s="5">
         <v>36</v>
@@ -4510,11 +4513,14 @@
       <c r="K40" s="5">
         <v>1.6</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="5">
+        <v>5000</v>
+      </c>
+      <c r="O40" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>11</v>
       </c>
@@ -4525,7 +4531,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="5">
-        <v>7000</v>
+        <v>21000</v>
       </c>
       <c r="E41" s="5">
         <v>32</v>
@@ -4548,11 +4554,14 @@
       <c r="K41" s="5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" s="5">
+        <v>7000</v>
+      </c>
+      <c r="O41" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>12</v>
       </c>
@@ -4563,7 +4572,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="5">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="E42" s="5">
         <v>29</v>
@@ -4586,11 +4595,14 @@
       <c r="K42" s="5">
         <v>3</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" s="5">
+        <v>9000</v>
+      </c>
+      <c r="O42" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>13</v>
       </c>
@@ -4601,7 +4613,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="5">
-        <v>11000</v>
+        <v>33000</v>
       </c>
       <c r="E43" s="5">
         <v>26</v>
@@ -4624,11 +4636,14 @@
       <c r="K43" s="5">
         <v>4</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="5">
+        <v>11000</v>
+      </c>
+      <c r="O43" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>14</v>
       </c>
@@ -4639,7 +4654,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="5">
-        <v>14000</v>
+        <v>42000</v>
       </c>
       <c r="E44" s="5">
         <v>23</v>
@@ -4662,11 +4677,14 @@
       <c r="K44" s="5">
         <v>5.4</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="5">
+        <v>14000</v>
+      </c>
+      <c r="O44" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>15</v>
       </c>
@@ -4677,7 +4695,8 @@
         <v>40</v>
       </c>
       <c r="D45" s="5">
-        <v>17000</v>
+        <f>M45*3</f>
+        <v>51000</v>
       </c>
       <c r="E45" s="5">
         <v>20</v>
@@ -4700,8 +4719,11 @@
       <c r="K45" s="5">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M45" s="5">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>16</v>
       </c>
@@ -4712,7 +4734,8 @@
         <v>41</v>
       </c>
       <c r="D46" s="5">
-        <v>20000</v>
+        <f t="shared" ref="D46:D51" si="2">M46*3</f>
+        <v>60000</v>
       </c>
       <c r="E46" s="5">
         <v>18</v>
@@ -4735,8 +4758,11 @@
       <c r="K46" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="M46" s="5">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>17</v>
       </c>
@@ -4747,7 +4773,8 @@
         <v>218</v>
       </c>
       <c r="D47" s="5">
-        <v>23000</v>
+        <f t="shared" si="2"/>
+        <v>69000</v>
       </c>
       <c r="E47" s="5">
         <v>16</v>
@@ -4770,14 +4797,17 @@
       <c r="K47" s="5">
         <v>10.8</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" s="5">
+        <v>23000</v>
+      </c>
+      <c r="O47" t="s">
         <v>223</v>
       </c>
-      <c r="N47">
+      <c r="P47">
         <v>500</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>18</v>
       </c>
@@ -4788,7 +4818,8 @@
         <v>219</v>
       </c>
       <c r="D48" s="5">
-        <v>26000</v>
+        <f t="shared" si="2"/>
+        <v>78000</v>
       </c>
       <c r="E48" s="5">
         <v>14</v>
@@ -4811,12 +4842,15 @@
       <c r="K48" s="5">
         <v>12.6</v>
       </c>
-      <c r="N48">
-        <f>N47*180</f>
+      <c r="M48" s="5">
+        <v>26000</v>
+      </c>
+      <c r="P48">
+        <f>P47*180</f>
         <v>90000</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>19</v>
       </c>
@@ -4827,7 +4861,7 @@
         <v>220</v>
       </c>
       <c r="D49" s="5">
-        <v>29000</v>
+        <v>100000</v>
       </c>
       <c r="E49" s="5">
         <v>12</v>
@@ -4850,8 +4884,11 @@
       <c r="K49" s="5">
         <v>14.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="M49" s="5">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>20</v>
       </c>
@@ -4862,7 +4899,7 @@
         <v>221</v>
       </c>
       <c r="D50" s="5">
-        <v>32000</v>
+        <v>200000</v>
       </c>
       <c r="E50" s="5">
         <v>10</v>
@@ -4885,8 +4922,11 @@
       <c r="K50" s="5">
         <v>16.2</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="M50" s="5">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>21</v>
       </c>
@@ -4897,7 +4937,7 @@
         <v>222</v>
       </c>
       <c r="D51" s="5">
-        <v>35000</v>
+        <v>300000</v>
       </c>
       <c r="E51" s="5">
         <v>8</v>
@@ -4920,8 +4960,11 @@
       <c r="K51" s="5">
         <v>18</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="M51" s="5">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>212</v>
       </c>
@@ -4929,7 +4972,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="C55" t="s">
         <v>45</v>
       </c>
@@ -4937,7 +4980,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>1</v>
       </c>
@@ -4954,12 +4997,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B57" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>2</v>
       </c>
@@ -4973,12 +5016,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>3</v>
       </c>
@@ -4992,7 +5035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
         <v>211</v>
       </c>
@@ -5393,7 +5436,7 @@
         <v>215</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" ref="L139:L140" si="2">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
+        <f t="shared" ref="L139:L140" si="3">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
         <v>調和は、犠牲に強く混沌に弱い。</v>
       </c>
     </row>
@@ -5414,7 +5457,7 @@
         <v>216</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>犠牲は、統制に強く調和に弱い。</v>
       </c>
     </row>
@@ -5917,5 +5960,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20162E1D-3031-4BCB-A997-D2DCF86D0814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D393339C-0852-4C55-B957-B1008AB7FC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2625" yWindow="405" windowWidth="20265" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="230">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -3008,6 +3008,22 @@
   </si>
   <si>
     <t>・雑魚敵夜限定強化更新　雑魚敵レベルが本来の+3になる　マップに設定のない場合、編成中キャラクターの一番レベルが高いキャラクター+3とする。　出現数が1.5倍になる　ウェーブ数が3になる　大きさが1.5倍になる　雑魚敵の攻撃射程が2倍になる　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　魔女出現時もレベルが同様に高レベルキャラクターの+5，HPは本来の2倍　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　　</t>
+  </si>
+  <si>
+    <t>時間進行（1日/時間帯進行ごと）</t>
+  </si>
+  <si>
+    <t>調整内容: ご要望通り 1〜3体（ランダム） の増加へとマイルドに調整したよ！</t>
+  </si>
+  <si>
+    <t>味方が増えたときの敵増加</t>
+  </si>
+  <si>
+    <t>戦闘時（ウェーブ内）: 主人公1人（単体）を基準として、仲間が1人増えるごとにウェーブ内敵数が +15体 加算される設定になっているよ！</t>
+  </si>
+  <si>
+    <t>マップ全体: 仲間が1人増えた瞬間に、全体の敵数が 1.２倍　+10＆ 敵レベルが +1 されるよ！</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -3425,7 +3441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25F42A9-A13E-41B6-8ACC-85810A7C82E6}">
-  <dimension ref="A2:AC208"/>
+  <dimension ref="A2:AC214"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9" customWidth="1"/>
@@ -5957,6 +5973,31 @@
         <v>224</v>
       </c>
     </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D393339C-0852-4C55-B957-B1008AB7FC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F568C-F640-48D7-A4D9-4848312A1CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="405" windowWidth="20265" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="870" yWindow="285" windowWidth="20640" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="235">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -2933,96 +2933,130 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>情熱</t>
-    <rPh sb="0" eb="2">
+    <t>魔女LV9</t>
+    <rPh sb="0" eb="2">
+      <t>マジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔女LV10</t>
+    <rPh sb="0" eb="2">
+      <t>マジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔女LV11</t>
+    <rPh sb="0" eb="2">
+      <t>マジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔女LV12</t>
+    <rPh sb="0" eb="2">
+      <t>マジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔女LV13</t>
+    <rPh sb="0" eb="2">
+      <t>マジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dps</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・雑魚敵夜限定強化更新　雑魚敵レベルが本来の+3になる　マップに設定のない場合、編成中キャラクターの一番レベルが高いキャラクター+3とする。　出現数が1.5倍になる　ウェーブ数が3になる　大きさが1.5倍になる　雑魚敵の攻撃射程が2倍になる　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　魔女出現時もレベルが同様に高レベルキャラクターの+5，HPは本来の2倍　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　　</t>
+  </si>
+  <si>
+    <t>時間進行（1日/時間帯進行ごと）</t>
+  </si>
+  <si>
+    <t>調整内容: ご要望通り 1〜3体（ランダム） の増加へとマイルドに調整したよ！</t>
+  </si>
+  <si>
+    <t>味方が増えたときの敵増加</t>
+  </si>
+  <si>
+    <t>戦闘時（ウェーブ内）: 主人公1人（単体）を基準として、仲間が1人増えるごとにウェーブ内敵数が +15体 加算される設定になっているよ！</t>
+  </si>
+  <si>
+    <t>マップ全体: 仲間が1人増えた瞬間に、全体の敵数が 1.２倍　+10＆ 敵レベルが +1 されるよ！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤い情熱</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>ジョウネツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>混沌</t>
-    <rPh sb="0" eb="2">
+    <t>紫の混沌</t>
+    <rPh sb="0" eb="1">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>コントン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>調和</t>
-    <rPh sb="0" eb="2">
+    <t>緑の調和</t>
+    <rPh sb="0" eb="1">
+      <t>ミドリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>チョウワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>犠牲</t>
-    <rPh sb="0" eb="2">
+    <t>黄色の犠牲</t>
+    <rPh sb="0" eb="2">
+      <t>キイロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>ギセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>統制</t>
-    <rPh sb="0" eb="2">
+    <t>青い統制</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>トウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>魔女LV9</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔女LV10</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔女LV11</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔女LV12</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔女LV13</t>
-    <rPh sb="0" eb="2">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>dps</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・雑魚敵夜限定強化更新　雑魚敵レベルが本来の+3になる　マップに設定のない場合、編成中キャラクターの一番レベルが高いキャラクター+3とする。　出現数が1.5倍になる　ウェーブ数が3になる　大きさが1.5倍になる　雑魚敵の攻撃射程が2倍になる　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　魔女出現時もレベルが同様に高レベルキャラクターの+5，HPは本来の2倍　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　　</t>
-  </si>
-  <si>
-    <t>時間進行（1日/時間帯進行ごと）</t>
-  </si>
-  <si>
-    <t>調整内容: ご要望通り 1〜3体（ランダム） の増加へとマイルドに調整したよ！</t>
-  </si>
-  <si>
-    <t>味方が増えたときの敵増加</t>
-  </si>
-  <si>
-    <t>戦闘時（ウェーブ内）: 主人公1人（単体）を基準として、仲間が1人増えるごとにウェーブ内敵数が +15体 加算される設定になっているよ！</t>
-  </si>
-  <si>
-    <t>マップ全体: 仲間が1人増えた瞬間に、全体の敵数が 1.２倍　+10＆ 敵レベルが +1 されるよ！</t>
+    <t>赤い情熱は、紫の混沌に強く青い統制に弱い。</t>
+  </si>
+  <si>
+    <t>紫の混沌は、緑の調和に強く赤い情熱に弱い。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>緑の調和は、黄色の犠牲に強く紫の混沌に弱い。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黄色の犠牲は、青い統制に強く緑の調和に弱い。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青い統制は、赤い情熱に強く黄色の犠牲に弱い。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4750,7 +4784,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="5">
-        <f t="shared" ref="D46:D51" si="2">M46*3</f>
+        <f t="shared" ref="D46:D48" si="2">M46*3</f>
         <v>60000</v>
       </c>
       <c r="E46" s="5">
@@ -4786,7 +4820,7 @@
         <v>9</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D47" s="5">
         <f t="shared" si="2"/>
@@ -4817,7 +4851,7 @@
         <v>23000</v>
       </c>
       <c r="O47" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P47">
         <v>500</v>
@@ -4831,7 +4865,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D48" s="5">
         <f t="shared" si="2"/>
@@ -4874,7 +4908,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D49" s="5">
         <v>100000</v>
@@ -4912,7 +4946,7 @@
         <v>12</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D50" s="5">
         <v>200000</v>
@@ -4950,7 +4984,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D51" s="5">
         <v>300000</v>
@@ -5407,11 +5441,11 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="L137" t="str">
         <f>K137&amp;"は、"&amp;K138&amp;"に強く"&amp;K141&amp;"に弱い。"</f>
-        <v>情熱は、混沌に強く統制に弱い。</v>
+        <v>赤い情熱は、紫の混沌に強く青い統制に弱い。</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.4">
@@ -5428,11 +5462,11 @@
         <v>255</v>
       </c>
       <c r="K138" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="L138" t="str">
         <f>K138&amp;"は、"&amp;K139&amp;"に強く"&amp;K137&amp;"に弱い。"</f>
-        <v>混沌は、調和に強く情熱に弱い。</v>
+        <v>紫の混沌は、緑の調和に強く赤い情熱に弱い。</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.4">
@@ -5449,11 +5483,11 @@
         <v>107</v>
       </c>
       <c r="K139" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L139" t="str">
         <f t="shared" ref="L139:L140" si="3">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
-        <v>調和は、犠牲に強く混沌に弱い。</v>
+        <v>緑の調和は、黄色の犠牲に強く紫の混沌に弱い。</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.4">
@@ -5470,11 +5504,11 @@
         <v>191</v>
       </c>
       <c r="K140" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="L140" t="str">
         <f t="shared" si="3"/>
-        <v>犠牲は、統制に強く調和に弱い。</v>
+        <v>黄色の犠牲は、青い統制に強く緑の調和に弱い。</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.4">
@@ -5494,36 +5528,51 @@
         <v>225</v>
       </c>
       <c r="K141" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L141" t="str">
         <f>K141&amp;"は、"&amp;K137&amp;"に強く"&amp;K140&amp;"に弱い。"</f>
-        <v>統制は、情熱に強く犠牲に弱い。</v>
+        <v>青い統制は、赤い情熱に強く黄色の犠牲に弱い。</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>101</v>
       </c>
+      <c r="L143" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>102</v>
       </c>
+      <c r="L144" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>103</v>
       </c>
+      <c r="L145" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>104</v>
       </c>
+      <c r="L146" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>105</v>
+      </c>
+      <c r="L147" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.4">
@@ -5970,32 +6019,32 @@
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F568C-F640-48D7-A4D9-4848312A1CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF2AE69-BAE6-489F-85B8-F8096E598B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="285" windowWidth="20640" windowHeight="14895" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="7995" yWindow="450" windowWidth="19005" windowHeight="14850" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="241">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -156,22 +157,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゴブリン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オーガ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コボルド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オーク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃頻度</t>
     <rPh sb="0" eb="4">
       <t>コウゲキヒンド</t>
@@ -179,22 +164,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スウォーム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フライ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マノウォー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゴーレム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デバフ抵抗</t>
     <rPh sb="3" eb="5">
       <t>テイコウ</t>
@@ -567,16 +536,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>雑魚の行動パヤーン</t>
-    <rPh sb="0" eb="2">
-      <t>ザコ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>進む方向が決まったらその方向に向かって(移動速度)で(移動距離)分進む。</t>
     <rPh sb="0" eb="1">
       <t>スス</t>
@@ -1376,53 +1335,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>en003-1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en003-2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en003-4</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スピリット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en003-3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en001-3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en002-4</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en001-1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en002-3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>en002-2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>使用グラフィック</t>
-    <rPh sb="0" eb="2">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>10ｍ以内に女の子がいるとそちらに向かって移動する。複数いれば最も近いものを選ぶ、そうでなければ下方向±10°の方向に進む。</t>
     <rPh sb="3" eb="5">
       <t>イナイ</t>
@@ -3058,13 +2970,91 @@
   <si>
     <t>青い統制は、赤い情熱に強く黄色の犠牲に弱い。</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スウォーム</t>
+  </si>
+  <si>
+    <t>フライ</t>
+  </si>
+  <si>
+    <t>スピリット</t>
+  </si>
+  <si>
+    <t>マノウォー</t>
+  </si>
+  <si>
+    <t>ゴブリン</t>
+  </si>
+  <si>
+    <t>コボルド</t>
+  </si>
+  <si>
+    <t>オーク</t>
+  </si>
+  <si>
+    <t>オーガ</t>
+  </si>
+  <si>
+    <t>ゴーレム</t>
+  </si>
+  <si>
+    <t>ID,名前,出現数,HP,移動速度,移動距離(m),移動間隔(秒),攻撃射程(m),攻撃頻度,攻撃力,重量,デバフ抵抗,大きさ,テクスチャ,フレーム</t>
+  </si>
+  <si>
+    <t>1,スウォーム,9,15,100,6.0,0.5,3.0,0.5,1,5,0,0.5,en003,0</t>
+  </si>
+  <si>
+    <t>2,フライ,4,30,75,4.5,0.45,4.0,0.5,1,10,0,0.75,en003,1</t>
+  </si>
+  <si>
+    <t>3,スピリット,8,50,55,6.0,0.4,4.0,0.5,1,45,50,1.0,en003,2</t>
+  </si>
+  <si>
+    <t>4,マノウォー,3,30,60,6.0,0.3,8.0,1.0,1,15,50,1.0,en003,3</t>
+  </si>
+  <si>
+    <t>5,ゴブリン,8,50,50,3.0,0.25,4.0,1.0,1,35,0,0.5,en001,2</t>
+  </si>
+  <si>
+    <t>6,コボルド,6,90,40,4.5,0.35,4.0,1.0,1,55,50,0.75,en002,3</t>
+  </si>
+  <si>
+    <t>7,オーク,6,90,30,3.9,0.5,8.0,2.0,1,75,0,0.75,en001,0</t>
+  </si>
+  <si>
+    <t>8,オーガ,3,125,25,3.6,0.35,8.0,2.0,1,110,50,1.0,en002,2</t>
+  </si>
+  <si>
+    <t>9,ゴーレム,1,250,25,3.6,0.6,8.0,2.0,1,110,50,1.25,en002,1</t>
+  </si>
+  <si>
+    <t>10,サンドバッグ,3,99999,0,0,99,0,99,0,1000,100,1.0,en001,1</t>
+  </si>
+  <si>
+    <t>en003</t>
+  </si>
+  <si>
+    <t>en001</t>
+  </si>
+  <si>
+    <t>en002</t>
+  </si>
+  <si>
+    <t>サンドバッグ</t>
+  </si>
+  <si>
+    <t>テクスチャ</t>
+  </si>
+  <si>
+    <t>フレーム</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3104,6 +3094,12 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3113,7 +3109,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3136,13 +3132,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3159,6 +3181,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3475,18 +3509,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25F42A9-A13E-41B6-8ACC-85810A7C82E6}">
-  <dimension ref="A2:AC214"/>
+  <dimension ref="A2:P226"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -3494,34 +3528,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A8" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
         <v>7</v>
       </c>
@@ -3538,7 +3572,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>8</v>
@@ -3547,80 +3581,42 @@
         <v>9</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC8" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
+        <v>239</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>1</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="5">
         <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="D9" s="5">
         <v>15</v>
       </c>
       <c r="E9" s="5">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5">
-        <f>U9*3</f>
         <v>6</v>
       </c>
       <c r="G9" s="5">
         <v>0.5</v>
       </c>
       <c r="H9" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="5">
         <v>0.5</v>
@@ -3638,76 +3634,36 @@
         <v>0.5</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="P9" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>9</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="S9" s="5">
-        <v>30</v>
-      </c>
-      <c r="T9" s="5">
-        <v>100</v>
-      </c>
-      <c r="U9" s="5">
-        <v>2</v>
-      </c>
-      <c r="V9" s="5">
-        <v>2</v>
-      </c>
-      <c r="W9" s="5">
-        <v>1</v>
-      </c>
-      <c r="X9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="Y9" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="5">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="5">
+        <v>235</v>
+      </c>
+      <c r="O9" s="5">
         <v>0</v>
       </c>
-      <c r="AB9" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>2</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="5">
         <v>4</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="D10" s="5">
         <v>30</v>
       </c>
       <c r="E10" s="5">
-        <v>75</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="5">
-        <f t="shared" ref="F10:F17" si="0">U10*3</f>
         <v>4.5</v>
       </c>
       <c r="G10" s="5">
         <v>0.45</v>
       </c>
       <c r="H10" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" s="5">
         <v>0.5</v>
@@ -3725,76 +3681,36 @@
         <v>0.75</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="P10" s="5">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>4</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S10" s="5">
-        <v>60</v>
-      </c>
-      <c r="T10" s="5">
-        <v>75</v>
-      </c>
-      <c r="U10" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="V10" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="W10" s="5">
-        <v>2</v>
-      </c>
-      <c r="X10" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="Y10" s="5">
+        <v>235</v>
+      </c>
+      <c r="O10" s="5">
         <v>1</v>
       </c>
-      <c r="Z10" s="5">
-        <v>10</v>
-      </c>
-      <c r="AA10" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="AC10" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="5">
         <v>8</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="D11" s="5">
         <v>50</v>
       </c>
       <c r="E11" s="5">
-        <v>55</v>
+        <v>1.6</v>
       </c>
       <c r="F11" s="5">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="G11" s="5">
         <v>0.4</v>
       </c>
       <c r="H11" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11" s="5">
         <v>0.5</v>
@@ -3812,73 +3728,33 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="P11" s="5">
+        <v>235</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A12" s="5">
         <v>4</v>
       </c>
-      <c r="Q11" s="5">
-        <v>8</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="S11" s="5">
-        <v>100</v>
-      </c>
-      <c r="T11" s="5">
-        <v>55</v>
-      </c>
-      <c r="U11" s="5">
-        <v>2</v>
-      </c>
-      <c r="V11" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="W11" s="5">
-        <v>2</v>
-      </c>
-      <c r="X11" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="Y11" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA11" s="5">
-        <v>50</v>
-      </c>
-      <c r="AB11" s="5">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
+      <c r="B12" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="5">
         <v>3</v>
-      </c>
-      <c r="B12" s="5">
-        <v>3</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
       </c>
       <c r="E12" s="5">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="5">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="5">
         <v>8</v>
@@ -3899,71 +3775,30 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="P12" s="5">
+        <v>235</v>
+      </c>
+      <c r="O12" s="5">
         <v>3</v>
       </c>
-      <c r="Q12" s="5">
-        <v>3</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="S12" s="5">
-        <v>60</v>
-      </c>
-      <c r="T12" s="5">
-        <v>60</v>
-      </c>
-      <c r="U12" s="5">
-        <v>2</v>
-      </c>
-      <c r="V12" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="W12" s="5">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A13" s="5">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="5">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5">
+        <v>50</v>
+      </c>
+      <c r="E13" s="5">
         <v>10</v>
       </c>
-      <c r="X12" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="5">
-        <v>15</v>
-      </c>
-      <c r="AA12" s="5">
-        <v>50</v>
-      </c>
-      <c r="AB12" s="5">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A13" s="5">
-        <v>4</v>
-      </c>
-      <c r="B13" s="5">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="5">
-        <f>S13/4</f>
-        <v>50</v>
-      </c>
-      <c r="E13" s="5">
-        <v>50</v>
-      </c>
       <c r="F13" s="5">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="5">
         <v>0.25</v>
@@ -3972,7 +3807,7 @@
         <v>4</v>
       </c>
       <c r="I13" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" s="5">
         <v>1</v>
@@ -3987,79 +3822,39 @@
         <v>0.5</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="P13" s="5">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>8</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="S13" s="5">
-        <v>200</v>
-      </c>
-      <c r="T13" s="5">
-        <v>50</v>
-      </c>
-      <c r="U13" s="5">
-        <v>1</v>
-      </c>
-      <c r="V13" s="5">
-        <v>1</v>
-      </c>
-      <c r="W13" s="5">
+        <v>236</v>
+      </c>
+      <c r="O13" s="5">
         <v>2</v>
       </c>
-      <c r="X13" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="5">
-        <v>35</v>
-      </c>
-      <c r="AA13" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
-        <v>5</v>
-      </c>
-      <c r="B14" s="5">
         <v>6</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>17</v>
+      <c r="B14" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="5">
+        <v>6</v>
       </c>
       <c r="D14" s="5">
         <v>90</v>
       </c>
       <c r="E14" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5">
         <v>0.35</v>
       </c>
       <c r="H14" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J14" s="5">
         <v>1</v>
@@ -4074,70 +3869,30 @@
         <v>0.75</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="P14" s="5">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="5">
+        <v>237</v>
+      </c>
+      <c r="O14" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A15" s="5">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="5">
         <v>6</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="S14" s="5">
-        <v>350</v>
-      </c>
-      <c r="T14" s="5">
-        <v>40</v>
-      </c>
-      <c r="U14" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="V14" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="W14" s="5">
-        <v>2</v>
-      </c>
-      <c r="X14" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="5">
-        <v>55</v>
-      </c>
-      <c r="AA14" s="5">
-        <v>50</v>
-      </c>
-      <c r="AB14" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="AC14" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A15" s="5">
-        <v>6</v>
-      </c>
-      <c r="B15" s="5">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="D15" s="5">
         <v>90</v>
       </c>
       <c r="E15" s="5">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="0"/>
-        <v>3.9000000000000004</v>
+        <v>0.9</v>
       </c>
       <c r="G15" s="5">
         <v>0.5</v>
@@ -4146,7 +3901,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="5">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J15" s="5">
         <v>1</v>
@@ -4161,71 +3916,30 @@
         <v>0.75</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="P15" s="5">
+        <v>236</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A16" s="5">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5">
+        <v>125</v>
+      </c>
+      <c r="E16" s="5">
         <v>6</v>
       </c>
-      <c r="Q15" s="5">
-        <v>6</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S15" s="5">
-        <v>350</v>
-      </c>
-      <c r="T15" s="5">
-        <v>30</v>
-      </c>
-      <c r="U15" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="V15" s="5">
-        <v>2</v>
-      </c>
-      <c r="W15" s="5">
-        <v>10</v>
-      </c>
-      <c r="X15" s="5">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>75</v>
-      </c>
-      <c r="AA15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="AC15" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A16" s="5">
-        <v>7</v>
-      </c>
-      <c r="B16" s="5">
-        <v>3</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="5">
-        <f t="shared" ref="D16:D17" si="1">S16/4</f>
-        <v>125</v>
-      </c>
-      <c r="E16" s="5">
-        <v>25</v>
-      </c>
       <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>1.25</v>
       </c>
       <c r="G16" s="5">
         <v>0.35</v>
@@ -4234,7 +3948,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="5">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="5">
         <v>1</v>
@@ -4249,80 +3963,39 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="P16" s="5">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="5">
-        <v>3</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="S16" s="5">
-        <v>500</v>
-      </c>
-      <c r="T16" s="5">
-        <v>25</v>
-      </c>
-      <c r="U16" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="V16" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="W16" s="5">
-        <v>10</v>
-      </c>
-      <c r="X16" s="5">
+        <v>237</v>
+      </c>
+      <c r="O16" s="5">
         <v>2</v>
       </c>
-      <c r="Y16" s="5">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A17" s="5">
+        <v>9</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="5">
         <v>1</v>
       </c>
-      <c r="Z16" s="5">
-        <v>110</v>
-      </c>
-      <c r="AA16" s="5">
-        <v>50</v>
-      </c>
-      <c r="AB16" s="5">
+      <c r="D17" s="5">
+        <v>250</v>
+      </c>
+      <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="AC16" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A17" s="5">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="5">
-        <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="E17" s="5">
-        <v>25</v>
-      </c>
       <c r="F17" s="5">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>3.6</v>
       </c>
       <c r="G17" s="5">
         <v>0.6</v>
       </c>
       <c r="H17" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="5">
         <v>1</v>
@@ -4337,1714 +4010,2218 @@
         <v>1.25</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="P17" s="5">
+        <v>237</v>
+      </c>
+      <c r="O17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A18" s="9">
+        <v>10</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="9">
+        <v>3</v>
+      </c>
+      <c r="D18" s="9">
+        <v>333333</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>99</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>99</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>1000</v>
+      </c>
+      <c r="L18" s="9">
+        <v>100</v>
+      </c>
+      <c r="M18" s="9">
+        <v>1</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="O18" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="K20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21" s="8">
+        <v>9</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="5">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5">
+        <v>50</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+      <c r="F21" s="5">
+        <v>6</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="5">
+        <v>4</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="5">
         <v>1</v>
       </c>
-      <c r="R17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="S17" s="5">
-        <v>1000</v>
-      </c>
-      <c r="T17" s="5">
-        <v>25</v>
-      </c>
-      <c r="U17" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="V17" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="W17" s="5">
+      <c r="K21" s="5">
+        <v>5</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A22" s="5">
         <v>10</v>
       </c>
-      <c r="X17" s="5">
+      <c r="B22" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="5">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>100</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F22" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="H22" s="5">
+        <v>6</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>10</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="O22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" s="5">
+        <v>11</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="5">
+        <v>8</v>
+      </c>
+      <c r="D23" s="5">
+        <v>150</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="F23" s="5">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H23" s="5">
+        <v>6</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
+        <v>45</v>
+      </c>
+      <c r="L23" s="5">
+        <v>50</v>
+      </c>
+      <c r="M23" s="5">
+        <v>1</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="O23" s="5">
         <v>2</v>
       </c>
-      <c r="Y17" s="5">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" s="5">
+        <v>12</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5">
+        <v>200</v>
+      </c>
+      <c r="E24" s="5">
         <v>1</v>
       </c>
-      <c r="Z17" s="5">
+      <c r="F24" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="5">
+        <v>8</v>
+      </c>
+      <c r="I24" s="5">
+        <v>1</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1</v>
+      </c>
+      <c r="K24" s="5">
+        <v>15</v>
+      </c>
+      <c r="L24" s="5">
+        <v>50</v>
+      </c>
+      <c r="M24" s="5">
+        <v>1</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="O24" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A25" s="5">
+        <v>13</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="5">
+        <v>8</v>
+      </c>
+      <c r="D25" s="5">
+        <v>100</v>
+      </c>
+      <c r="E25" s="5">
+        <v>10</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="H25" s="5">
+        <v>4</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5">
+        <v>35</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="O25" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A26" s="5">
+        <v>14</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="5">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>120</v>
+      </c>
+      <c r="E26" s="5">
+        <v>8</v>
+      </c>
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="H26" s="5">
+        <v>6</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <v>55</v>
+      </c>
+      <c r="L26" s="5">
+        <v>50</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="O26" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A27" s="5">
+        <v>15</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C27" s="5">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5">
+        <v>140</v>
+      </c>
+      <c r="E27" s="5">
+        <v>7</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="5">
+        <v>8</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5">
+        <v>75</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="O27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A28" s="5">
+        <v>16</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="5">
+        <v>3</v>
+      </c>
+      <c r="D28" s="5">
+        <v>180</v>
+      </c>
+      <c r="E28" s="5">
+        <v>6</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="H28" s="5">
+        <v>8</v>
+      </c>
+      <c r="I28" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="5">
         <v>110</v>
       </c>
-      <c r="AA17" s="5">
+      <c r="L28" s="5">
         <v>50</v>
       </c>
-      <c r="AB17" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+      <c r="M28" s="5">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="O28" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="5">
+        <v>17</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
+        <v>250</v>
+      </c>
+      <c r="E29" s="5">
+        <v>2</v>
+      </c>
+      <c r="F29" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H29" s="5">
+        <v>4</v>
+      </c>
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <v>110</v>
+      </c>
+      <c r="L29" s="5">
+        <v>50</v>
+      </c>
+      <c r="M29" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="O29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A38" s="5" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A50" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5" t="s">
+      <c r="B50" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F50" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H50" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A39" s="5">
+      <c r="J50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O50" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A51" s="5">
         <v>9</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B51" s="5">
         <v>1</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="5">
         <v>9000</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E51" s="5">
         <v>40</v>
-      </c>
-      <c r="F39" s="5">
-        <v>2</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="H39" s="5">
-        <v>15</v>
-      </c>
-      <c r="I39" s="5">
-        <v>15</v>
-      </c>
-      <c r="J39" s="5">
-        <v>100</v>
-      </c>
-      <c r="K39" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="M39" s="5">
-        <v>3000</v>
-      </c>
-      <c r="O39" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A40" s="5">
-        <v>10</v>
-      </c>
-      <c r="B40" s="5">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E40" s="5">
-        <v>36</v>
-      </c>
-      <c r="F40" s="5">
-        <v>2</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="5">
-        <v>17</v>
-      </c>
-      <c r="I40" s="5">
-        <v>36</v>
-      </c>
-      <c r="J40" s="5">
-        <v>100</v>
-      </c>
-      <c r="K40" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="M40" s="5">
-        <v>5000</v>
-      </c>
-      <c r="O40" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A41" s="5">
-        <v>11</v>
-      </c>
-      <c r="B41" s="5">
-        <v>3</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="5">
-        <v>21000</v>
-      </c>
-      <c r="E41" s="5">
-        <v>32</v>
-      </c>
-      <c r="F41" s="5">
-        <v>2</v>
-      </c>
-      <c r="G41" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="H41" s="5">
-        <v>19</v>
-      </c>
-      <c r="I41" s="5">
-        <v>90</v>
-      </c>
-      <c r="J41" s="5">
-        <v>100</v>
-      </c>
-      <c r="K41" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M41" s="5">
-        <v>7000</v>
-      </c>
-      <c r="O41" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A42" s="5">
-        <v>12</v>
-      </c>
-      <c r="B42" s="5">
-        <v>4</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="5">
-        <v>27000</v>
-      </c>
-      <c r="E42" s="5">
-        <v>29</v>
-      </c>
-      <c r="F42" s="5">
-        <v>2</v>
-      </c>
-      <c r="G42" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="H42" s="5">
-        <v>21</v>
-      </c>
-      <c r="I42" s="5">
-        <v>223</v>
-      </c>
-      <c r="J42" s="5">
-        <v>100</v>
-      </c>
-      <c r="K42" s="5">
-        <v>3</v>
-      </c>
-      <c r="M42" s="5">
-        <v>9000</v>
-      </c>
-      <c r="O42" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A43" s="5">
-        <v>13</v>
-      </c>
-      <c r="B43" s="5">
-        <v>5</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="5">
-        <v>33000</v>
-      </c>
-      <c r="E43" s="5">
-        <v>26</v>
-      </c>
-      <c r="F43" s="5">
-        <v>2</v>
-      </c>
-      <c r="G43" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="H43" s="5">
-        <v>23</v>
-      </c>
-      <c r="I43" s="5">
-        <v>550</v>
-      </c>
-      <c r="J43" s="5">
-        <v>100</v>
-      </c>
-      <c r="K43" s="5">
-        <v>4</v>
-      </c>
-      <c r="M43" s="5">
-        <v>11000</v>
-      </c>
-      <c r="O43" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A44" s="5">
-        <v>14</v>
-      </c>
-      <c r="B44" s="5">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="5">
-        <v>42000</v>
-      </c>
-      <c r="E44" s="5">
-        <v>23</v>
-      </c>
-      <c r="F44" s="5">
-        <v>2</v>
-      </c>
-      <c r="G44" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="H44" s="5">
-        <v>25</v>
-      </c>
-      <c r="I44" s="5">
-        <v>1350</v>
-      </c>
-      <c r="J44" s="5">
-        <v>100</v>
-      </c>
-      <c r="K44" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="M44" s="5">
-        <v>14000</v>
-      </c>
-      <c r="O44" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A45" s="5">
-        <v>15</v>
-      </c>
-      <c r="B45" s="5">
-        <v>7</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="5">
-        <f>M45*3</f>
-        <v>51000</v>
-      </c>
-      <c r="E45" s="5">
-        <v>20</v>
-      </c>
-      <c r="F45" s="5">
-        <v>2</v>
-      </c>
-      <c r="G45" s="5">
-        <v>1</v>
-      </c>
-      <c r="H45" s="5">
-        <v>27</v>
-      </c>
-      <c r="I45" s="5">
-        <v>3300</v>
-      </c>
-      <c r="J45" s="5">
-        <v>100</v>
-      </c>
-      <c r="K45" s="5">
-        <v>7.2</v>
-      </c>
-      <c r="M45" s="5">
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A46" s="5">
-        <v>16</v>
-      </c>
-      <c r="B46" s="5">
-        <v>8</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D46" s="5">
-        <f t="shared" ref="D46:D48" si="2">M46*3</f>
-        <v>60000</v>
-      </c>
-      <c r="E46" s="5">
-        <v>18</v>
-      </c>
-      <c r="F46" s="5">
-        <v>2</v>
-      </c>
-      <c r="G46" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="H46" s="5">
-        <v>29</v>
-      </c>
-      <c r="I46" s="5">
-        <v>8000</v>
-      </c>
-      <c r="J46" s="5">
-        <v>100</v>
-      </c>
-      <c r="K46" s="5">
-        <v>9</v>
-      </c>
-      <c r="M46" s="5">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A47" s="5">
-        <v>17</v>
-      </c>
-      <c r="B47" s="5">
-        <v>9</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D47" s="5">
-        <f t="shared" si="2"/>
-        <v>69000</v>
-      </c>
-      <c r="E47" s="5">
-        <v>16</v>
-      </c>
-      <c r="F47" s="5">
-        <v>2</v>
-      </c>
-      <c r="G47" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="H47" s="5">
-        <v>31</v>
-      </c>
-      <c r="I47" s="5">
-        <v>12700</v>
-      </c>
-      <c r="J47" s="5">
-        <v>100</v>
-      </c>
-      <c r="K47" s="5">
-        <v>10.8</v>
-      </c>
-      <c r="M47" s="5">
-        <v>23000</v>
-      </c>
-      <c r="O47" t="s">
-        <v>218</v>
-      </c>
-      <c r="P47">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A48" s="5">
-        <v>18</v>
-      </c>
-      <c r="B48" s="5">
-        <v>10</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" s="5">
-        <f t="shared" si="2"/>
-        <v>78000</v>
-      </c>
-      <c r="E48" s="5">
-        <v>14</v>
-      </c>
-      <c r="F48" s="5">
-        <v>2</v>
-      </c>
-      <c r="G48" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="H48" s="5">
-        <v>33</v>
-      </c>
-      <c r="I48" s="5">
-        <v>17400</v>
-      </c>
-      <c r="J48" s="5">
-        <v>100</v>
-      </c>
-      <c r="K48" s="5">
-        <v>12.6</v>
-      </c>
-      <c r="M48" s="5">
-        <v>26000</v>
-      </c>
-      <c r="P48">
-        <f>P47*180</f>
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A49" s="5">
-        <v>19</v>
-      </c>
-      <c r="B49" s="5">
-        <v>11</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D49" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E49" s="5">
-        <v>12</v>
-      </c>
-      <c r="F49" s="5">
-        <v>2</v>
-      </c>
-      <c r="G49" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="H49" s="5">
-        <v>35</v>
-      </c>
-      <c r="I49" s="5">
-        <v>22100</v>
-      </c>
-      <c r="J49" s="5">
-        <v>100</v>
-      </c>
-      <c r="K49" s="5">
-        <v>14.4</v>
-      </c>
-      <c r="M49" s="5">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A50" s="5">
-        <v>20</v>
-      </c>
-      <c r="B50" s="5">
-        <v>12</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D50" s="5">
-        <v>200000</v>
-      </c>
-      <c r="E50" s="5">
-        <v>10</v>
-      </c>
-      <c r="F50" s="5">
-        <v>2</v>
-      </c>
-      <c r="G50" s="5">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5">
-        <v>37</v>
-      </c>
-      <c r="I50" s="5">
-        <v>26800</v>
-      </c>
-      <c r="J50" s="5">
-        <v>100</v>
-      </c>
-      <c r="K50" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="M50" s="5">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A51" s="5">
-        <v>21</v>
-      </c>
-      <c r="B51" s="5">
-        <v>13</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D51" s="5">
-        <v>300000</v>
-      </c>
-      <c r="E51" s="5">
-        <v>8</v>
       </c>
       <c r="F51" s="5">
         <v>2</v>
       </c>
       <c r="G51" s="5">
-        <v>2.2000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="H51" s="5">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="I51" s="5">
-        <v>31500</v>
+        <v>15</v>
       </c>
       <c r="J51" s="5">
         <v>100</v>
       </c>
       <c r="K51" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="M51" s="5">
+        <v>3000</v>
+      </c>
+      <c r="O51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A52" s="5">
+        <v>10</v>
+      </c>
+      <c r="B52" s="5">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="5">
+        <v>36</v>
+      </c>
+      <c r="F52" s="5">
+        <v>2</v>
+      </c>
+      <c r="G52" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H52" s="5">
+        <v>17</v>
+      </c>
+      <c r="I52" s="5">
+        <v>36</v>
+      </c>
+      <c r="J52" s="5">
+        <v>100</v>
+      </c>
+      <c r="K52" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="M52" s="5">
+        <v>5000</v>
+      </c>
+      <c r="O52" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A53" s="5">
+        <v>11</v>
+      </c>
+      <c r="B53" s="5">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="5">
+        <v>21000</v>
+      </c>
+      <c r="E53" s="5">
+        <v>32</v>
+      </c>
+      <c r="F53" s="5">
+        <v>2</v>
+      </c>
+      <c r="G53" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H53" s="5">
+        <v>19</v>
+      </c>
+      <c r="I53" s="5">
+        <v>90</v>
+      </c>
+      <c r="J53" s="5">
+        <v>100</v>
+      </c>
+      <c r="K53" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M53" s="5">
+        <v>7000</v>
+      </c>
+      <c r="O53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A54" s="5">
+        <v>12</v>
+      </c>
+      <c r="B54" s="5">
+        <v>4</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="5">
+        <v>27000</v>
+      </c>
+      <c r="E54" s="5">
+        <v>29</v>
+      </c>
+      <c r="F54" s="5">
+        <v>2</v>
+      </c>
+      <c r="G54" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="H54" s="5">
+        <v>21</v>
+      </c>
+      <c r="I54" s="5">
+        <v>223</v>
+      </c>
+      <c r="J54" s="5">
+        <v>100</v>
+      </c>
+      <c r="K54" s="5">
+        <v>3</v>
+      </c>
+      <c r="M54" s="5">
+        <v>9000</v>
+      </c>
+      <c r="O54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A55" s="5">
+        <v>13</v>
+      </c>
+      <c r="B55" s="5">
+        <v>5</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="5">
+        <v>33000</v>
+      </c>
+      <c r="E55" s="5">
+        <v>26</v>
+      </c>
+      <c r="F55" s="5">
+        <v>2</v>
+      </c>
+      <c r="G55" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="H55" s="5">
+        <v>23</v>
+      </c>
+      <c r="I55" s="5">
+        <v>550</v>
+      </c>
+      <c r="J55" s="5">
+        <v>100</v>
+      </c>
+      <c r="K55" s="5">
+        <v>4</v>
+      </c>
+      <c r="M55" s="5">
+        <v>11000</v>
+      </c>
+      <c r="O55" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A56" s="5">
+        <v>14</v>
+      </c>
+      <c r="B56" s="5">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="5">
+        <v>42000</v>
+      </c>
+      <c r="E56" s="5">
+        <v>23</v>
+      </c>
+      <c r="F56" s="5">
+        <v>2</v>
+      </c>
+      <c r="G56" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H56" s="5">
+        <v>25</v>
+      </c>
+      <c r="I56" s="5">
+        <v>1350</v>
+      </c>
+      <c r="J56" s="5">
+        <v>100</v>
+      </c>
+      <c r="K56" s="5">
+        <v>5.4</v>
+      </c>
+      <c r="M56" s="5">
+        <v>14000</v>
+      </c>
+      <c r="O56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A57" s="5">
+        <v>15</v>
+      </c>
+      <c r="B57" s="5">
+        <v>7</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="5">
+        <f>M57*3</f>
+        <v>51000</v>
+      </c>
+      <c r="E57" s="5">
+        <v>20</v>
+      </c>
+      <c r="F57" s="5">
+        <v>2</v>
+      </c>
+      <c r="G57" s="5">
+        <v>1</v>
+      </c>
+      <c r="H57" s="5">
+        <v>27</v>
+      </c>
+      <c r="I57" s="5">
+        <v>3300</v>
+      </c>
+      <c r="J57" s="5">
+        <v>100</v>
+      </c>
+      <c r="K57" s="5">
+        <v>7.2</v>
+      </c>
+      <c r="M57" s="5">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A58" s="5">
+        <v>16</v>
+      </c>
+      <c r="B58" s="5">
+        <v>8</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="5">
+        <f t="shared" ref="D58:D60" si="0">M58*3</f>
+        <v>60000</v>
+      </c>
+      <c r="E58" s="5">
         <v>18</v>
       </c>
-      <c r="M51" s="5">
+      <c r="F58" s="5">
+        <v>2</v>
+      </c>
+      <c r="G58" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="H58" s="5">
+        <v>29</v>
+      </c>
+      <c r="I58" s="5">
+        <v>8000</v>
+      </c>
+      <c r="J58" s="5">
+        <v>100</v>
+      </c>
+      <c r="K58" s="5">
+        <v>9</v>
+      </c>
+      <c r="M58" s="5">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A59" s="5">
+        <v>17</v>
+      </c>
+      <c r="B59" s="5">
+        <v>9</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" s="5">
+        <f t="shared" si="0"/>
+        <v>69000</v>
+      </c>
+      <c r="E59" s="5">
+        <v>16</v>
+      </c>
+      <c r="F59" s="5">
+        <v>2</v>
+      </c>
+      <c r="G59" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="H59" s="5">
+        <v>31</v>
+      </c>
+      <c r="I59" s="5">
+        <v>12700</v>
+      </c>
+      <c r="J59" s="5">
+        <v>100</v>
+      </c>
+      <c r="K59" s="5">
+        <v>10.8</v>
+      </c>
+      <c r="M59" s="5">
+        <v>23000</v>
+      </c>
+      <c r="O59" t="s">
+        <v>198</v>
+      </c>
+      <c r="P59">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A60" s="5">
+        <v>18</v>
+      </c>
+      <c r="B60" s="5">
+        <v>10</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60" s="5">
+        <f t="shared" si="0"/>
+        <v>78000</v>
+      </c>
+      <c r="E60" s="5">
+        <v>14</v>
+      </c>
+      <c r="F60" s="5">
+        <v>2</v>
+      </c>
+      <c r="G60" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="H60" s="5">
+        <v>33</v>
+      </c>
+      <c r="I60" s="5">
+        <v>17400</v>
+      </c>
+      <c r="J60" s="5">
+        <v>100</v>
+      </c>
+      <c r="K60" s="5">
+        <v>12.6</v>
+      </c>
+      <c r="M60" s="5">
+        <v>26000</v>
+      </c>
+      <c r="P60">
+        <f>P59*180</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A61" s="5">
+        <v>19</v>
+      </c>
+      <c r="B61" s="5">
+        <v>11</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E61" s="5">
+        <v>12</v>
+      </c>
+      <c r="F61" s="5">
+        <v>2</v>
+      </c>
+      <c r="G61" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="H61" s="5">
+        <v>35</v>
+      </c>
+      <c r="I61" s="5">
+        <v>22100</v>
+      </c>
+      <c r="J61" s="5">
+        <v>100</v>
+      </c>
+      <c r="K61" s="5">
+        <v>14.4</v>
+      </c>
+      <c r="M61" s="5">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A62" s="5">
+        <v>20</v>
+      </c>
+      <c r="B62" s="5">
+        <v>12</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" s="5">
+        <v>200000</v>
+      </c>
+      <c r="E62" s="5">
+        <v>10</v>
+      </c>
+      <c r="F62" s="5">
+        <v>2</v>
+      </c>
+      <c r="G62" s="5">
+        <v>2</v>
+      </c>
+      <c r="H62" s="5">
+        <v>37</v>
+      </c>
+      <c r="I62" s="5">
+        <v>26800</v>
+      </c>
+      <c r="J62" s="5">
+        <v>100</v>
+      </c>
+      <c r="K62" s="5">
+        <v>16.2</v>
+      </c>
+      <c r="M62" s="5">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A63" s="5">
+        <v>21</v>
+      </c>
+      <c r="B63" s="5">
+        <v>13</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E63" s="5">
+        <v>8</v>
+      </c>
+      <c r="F63" s="5">
+        <v>2</v>
+      </c>
+      <c r="G63" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H63" s="5">
+        <v>39</v>
+      </c>
+      <c r="I63" s="5">
+        <v>31500</v>
+      </c>
+      <c r="J63" s="5">
+        <v>100</v>
+      </c>
+      <c r="K63" s="5">
+        <v>18</v>
+      </c>
+      <c r="M63" s="5">
         <v>35000</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>212</v>
-      </c>
-      <c r="C54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="C55" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B69" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B72" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" t="s">
+        <v>42</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B75" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B77" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B78" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B79" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B80" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>4</v>
+      </c>
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B84" t="s">
+        <v>185</v>
+      </c>
+      <c r="C84" s="3"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B86" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87" t="s">
+        <v>44</v>
+      </c>
+      <c r="C87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B88" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
         <v>45</v>
       </c>
-      <c r="D55" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A56">
+      <c r="C89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B90" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="4"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A95">
         <v>1</v>
       </c>
-      <c r="B56" t="s">
-        <v>44</v>
-      </c>
-      <c r="C56" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B57" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A59">
+      <c r="B95" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A96">
         <v>2</v>
       </c>
-      <c r="B59" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" t="s">
-        <v>46</v>
-      </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B60" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A62">
+      <c r="B96" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A97">
         <v>3</v>
       </c>
-      <c r="B62" t="s">
-        <v>49</v>
-      </c>
-      <c r="C62" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="B63" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B65" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B66" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B67" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B68" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B69" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A71">
-        <v>4</v>
-      </c>
-      <c r="B71" t="s">
-        <v>28</v>
-      </c>
-      <c r="C71" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B72" t="s">
-        <v>205</v>
-      </c>
-      <c r="C72" s="3"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A73">
-        <v>5</v>
-      </c>
-      <c r="B73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B74" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A75">
-        <v>6</v>
-      </c>
-      <c r="B75" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B76" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A77">
-        <v>7</v>
-      </c>
-      <c r="B77" t="s">
-        <v>53</v>
-      </c>
-      <c r="C77" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B78" t="s">
-        <v>207</v>
-      </c>
-      <c r="C78" s="4"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A83">
-        <v>1</v>
-      </c>
-      <c r="B83" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A84">
-        <v>2</v>
-      </c>
-      <c r="B84" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A85">
-        <v>3</v>
-      </c>
-      <c r="B85" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A88" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A90" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A91" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A92" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A93" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
+      <c r="B97" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
-        <v>78</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>86</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>86</v>
+      </c>
+      <c r="F148" t="s">
+        <v>120</v>
+      </c>
+      <c r="G148" t="s">
+        <v>121</v>
+      </c>
+      <c r="H148" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>98</v>
+      </c>
+      <c r="B149" t="s">
+        <v>87</v>
+      </c>
+      <c r="F149">
+        <v>139</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="K149" t="s">
+        <v>205</v>
+      </c>
+      <c r="L149" t="str">
+        <f>K149&amp;"は、"&amp;K150&amp;"に強く"&amp;K153&amp;"に弱い。"</f>
+        <v>赤い情熱は、紫の混沌に強く青い統制に弱い。</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>100</v>
+      </c>
+      <c r="B150" t="s">
+        <v>91</v>
+      </c>
+      <c r="F150">
+        <v>255</v>
+      </c>
+      <c r="H150">
+        <v>255</v>
+      </c>
+      <c r="K150" t="s">
+        <v>206</v>
+      </c>
+      <c r="L150" t="str">
+        <f>K150&amp;"は、"&amp;K151&amp;"に強く"&amp;K149&amp;"に弱い。"</f>
+        <v>紫の混沌は、緑の調和に強く赤い情熱に弱い。</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>101</v>
+      </c>
+      <c r="B151" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A130" t="s">
+      <c r="G151">
+        <v>168</v>
+      </c>
+      <c r="H151">
+        <v>107</v>
+      </c>
+      <c r="K151" t="s">
+        <v>207</v>
+      </c>
+      <c r="L151" t="str">
+        <f t="shared" ref="L151:L152" si="1">K151&amp;"は、"&amp;K152&amp;"に強く"&amp;K150&amp;"に弱い。"</f>
+        <v>緑の調和は、黄色の犠牲に強く紫の混沌に弱い。</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>108</v>
+      </c>
+      <c r="B152" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A131" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A132" t="s">
+      <c r="F152">
+        <v>255</v>
+      </c>
+      <c r="G152">
+        <v>191</v>
+      </c>
+      <c r="K152" t="s">
+        <v>208</v>
+      </c>
+      <c r="L152" t="str">
+        <f t="shared" si="1"/>
+        <v>黄色の犠牲は、青い統制に強く緑の調和に弱い。</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>99</v>
+      </c>
+      <c r="B153" t="s">
+        <v>88</v>
+      </c>
+      <c r="F153">
+        <v>65</v>
+      </c>
+      <c r="G153">
+        <v>105</v>
+      </c>
+      <c r="H153">
+        <v>225</v>
+      </c>
+      <c r="K153" t="s">
+        <v>209</v>
+      </c>
+      <c r="L153" t="str">
+        <f>K153&amp;"は、"&amp;K149&amp;"に強く"&amp;K152&amp;"に弱い。"</f>
+        <v>青い統制は、赤い情熱に強く黄色の犠牲に弱い。</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A133" t="s">
+      <c r="L155" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A134" t="s">
+      <c r="L156" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A136" t="s">
+      <c r="L157" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
         <v>95</v>
       </c>
-      <c r="F136" t="s">
+      <c r="L158" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>96</v>
+      </c>
+      <c r="L159" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>112</v>
+      </c>
+      <c r="H163" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A164" s="5"/>
+      <c r="B164" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H164" s="5"/>
+      <c r="I164" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J164" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K164" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L164" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="M164" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A165" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B165" s="5">
+        <v>100</v>
+      </c>
+      <c r="C165" s="5">
+        <v>75</v>
+      </c>
+      <c r="D165" s="5">
+        <v>100</v>
+      </c>
+      <c r="E165" s="5">
+        <v>100</v>
+      </c>
+      <c r="F165" s="5">
+        <v>125</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I165" s="5">
+        <v>30</v>
+      </c>
+      <c r="J165" s="5">
+        <v>5</v>
+      </c>
+      <c r="K165" s="5">
+        <v>30</v>
+      </c>
+      <c r="L165" s="5">
+        <v>30</v>
+      </c>
+      <c r="M165" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A166" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B166" s="5">
+        <v>125</v>
+      </c>
+      <c r="C166" s="5">
+        <v>100</v>
+      </c>
+      <c r="D166" s="5">
+        <v>75</v>
+      </c>
+      <c r="E166" s="5">
+        <v>100</v>
+      </c>
+      <c r="F166" s="5">
+        <v>100</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I166" s="5">
+        <v>55</v>
+      </c>
+      <c r="J166" s="5">
+        <v>30</v>
+      </c>
+      <c r="K166" s="5">
+        <v>5</v>
+      </c>
+      <c r="L166" s="5">
+        <v>30</v>
+      </c>
+      <c r="M166" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A167" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B167" s="5">
+        <v>100</v>
+      </c>
+      <c r="C167" s="5">
+        <v>125</v>
+      </c>
+      <c r="D167" s="5">
+        <v>100</v>
+      </c>
+      <c r="E167" s="5">
+        <v>75</v>
+      </c>
+      <c r="F167" s="5">
+        <v>100</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I167" s="5">
+        <v>30</v>
+      </c>
+      <c r="J167" s="5">
+        <v>55</v>
+      </c>
+      <c r="K167" s="5">
+        <v>30</v>
+      </c>
+      <c r="L167" s="5">
+        <v>5</v>
+      </c>
+      <c r="M167" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A168" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B168" s="5">
+        <v>100</v>
+      </c>
+      <c r="C168" s="5">
+        <v>100</v>
+      </c>
+      <c r="D168" s="5">
+        <v>125</v>
+      </c>
+      <c r="E168" s="5">
+        <v>100</v>
+      </c>
+      <c r="F168" s="5">
+        <v>75</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I168" s="5">
+        <v>30</v>
+      </c>
+      <c r="J168" s="5">
+        <v>30</v>
+      </c>
+      <c r="K168" s="5">
+        <v>55</v>
+      </c>
+      <c r="L168" s="5">
+        <v>30</v>
+      </c>
+      <c r="M168" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A169" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B169" s="5">
+        <v>75</v>
+      </c>
+      <c r="C169" s="5">
+        <v>100</v>
+      </c>
+      <c r="D169" s="5">
+        <v>100</v>
+      </c>
+      <c r="E169" s="5">
+        <v>125</v>
+      </c>
+      <c r="F169" s="5">
+        <v>100</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I169" s="5">
+        <v>5</v>
+      </c>
+      <c r="J169" s="5">
+        <v>30</v>
+      </c>
+      <c r="K169" s="5">
+        <v>30</v>
+      </c>
+      <c r="L169" s="5">
+        <v>55</v>
+      </c>
+      <c r="M169" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>109</v>
+      </c>
+      <c r="H171" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>110</v>
+      </c>
+      <c r="H172" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
         <v>129</v>
       </c>
-      <c r="G136" t="s">
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
         <v>130</v>
-      </c>
-      <c r="H136" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A137" t="s">
-        <v>107</v>
-      </c>
-      <c r="B137" t="s">
-        <v>96</v>
-      </c>
-      <c r="F137">
-        <v>139</v>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="K137" t="s">
-        <v>225</v>
-      </c>
-      <c r="L137" t="str">
-        <f>K137&amp;"は、"&amp;K138&amp;"に強く"&amp;K141&amp;"に弱い。"</f>
-        <v>赤い情熱は、紫の混沌に強く青い統制に弱い。</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A138" t="s">
-        <v>109</v>
-      </c>
-      <c r="B138" t="s">
-        <v>100</v>
-      </c>
-      <c r="F138">
-        <v>255</v>
-      </c>
-      <c r="H138">
-        <v>255</v>
-      </c>
-      <c r="K138" t="s">
-        <v>226</v>
-      </c>
-      <c r="L138" t="str">
-        <f>K138&amp;"は、"&amp;K139&amp;"に強く"&amp;K137&amp;"に弱い。"</f>
-        <v>紫の混沌は、緑の調和に強く赤い情熱に弱い。</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A139" t="s">
-        <v>110</v>
-      </c>
-      <c r="B139" t="s">
-        <v>98</v>
-      </c>
-      <c r="G139">
-        <v>168</v>
-      </c>
-      <c r="H139">
-        <v>107</v>
-      </c>
-      <c r="K139" t="s">
-        <v>227</v>
-      </c>
-      <c r="L139" t="str">
-        <f t="shared" ref="L139:L140" si="3">K139&amp;"は、"&amp;K140&amp;"に強く"&amp;K138&amp;"に弱い。"</f>
-        <v>緑の調和は、黄色の犠牲に強く紫の混沌に弱い。</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A140" t="s">
-        <v>117</v>
-      </c>
-      <c r="B140" t="s">
-        <v>99</v>
-      </c>
-      <c r="F140">
-        <v>255</v>
-      </c>
-      <c r="G140">
-        <v>191</v>
-      </c>
-      <c r="K140" t="s">
-        <v>228</v>
-      </c>
-      <c r="L140" t="str">
-        <f t="shared" si="3"/>
-        <v>黄色の犠牲は、青い統制に強く緑の調和に弱い。</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A141" t="s">
-        <v>108</v>
-      </c>
-      <c r="B141" t="s">
-        <v>97</v>
-      </c>
-      <c r="F141">
-        <v>65</v>
-      </c>
-      <c r="G141">
-        <v>105</v>
-      </c>
-      <c r="H141">
-        <v>225</v>
-      </c>
-      <c r="K141" t="s">
-        <v>229</v>
-      </c>
-      <c r="L141" t="str">
-        <f>K141&amp;"は、"&amp;K137&amp;"に強く"&amp;K140&amp;"に弱い。"</f>
-        <v>青い統制は、赤い情熱に強く黄色の犠牲に弱い。</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A143" t="s">
-        <v>101</v>
-      </c>
-      <c r="L143" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A144" t="s">
-        <v>102</v>
-      </c>
-      <c r="L144" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A145" t="s">
-        <v>103</v>
-      </c>
-      <c r="L145" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A146" t="s">
-        <v>104</v>
-      </c>
-      <c r="L146" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A147" t="s">
-        <v>105</v>
-      </c>
-      <c r="L147" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A148" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A151" t="s">
-        <v>121</v>
-      </c>
-      <c r="H151" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H152" s="5"/>
-      <c r="I152" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="J152" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="K152" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L152" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="M152" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A153" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B153" s="5">
-        <v>100</v>
-      </c>
-      <c r="C153" s="5">
-        <v>75</v>
-      </c>
-      <c r="D153" s="5">
-        <v>100</v>
-      </c>
-      <c r="E153" s="5">
-        <v>100</v>
-      </c>
-      <c r="F153" s="5">
-        <v>125</v>
-      </c>
-      <c r="H153" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I153" s="5">
-        <v>30</v>
-      </c>
-      <c r="J153" s="5">
-        <v>5</v>
-      </c>
-      <c r="K153" s="5">
-        <v>30</v>
-      </c>
-      <c r="L153" s="5">
-        <v>30</v>
-      </c>
-      <c r="M153" s="5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A154" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B154" s="5">
-        <v>125</v>
-      </c>
-      <c r="C154" s="5">
-        <v>100</v>
-      </c>
-      <c r="D154" s="5">
-        <v>75</v>
-      </c>
-      <c r="E154" s="5">
-        <v>100</v>
-      </c>
-      <c r="F154" s="5">
-        <v>100</v>
-      </c>
-      <c r="H154" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I154" s="5">
-        <v>55</v>
-      </c>
-      <c r="J154" s="5">
-        <v>30</v>
-      </c>
-      <c r="K154" s="5">
-        <v>5</v>
-      </c>
-      <c r="L154" s="5">
-        <v>30</v>
-      </c>
-      <c r="M154" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A155" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B155" s="5">
-        <v>100</v>
-      </c>
-      <c r="C155" s="5">
-        <v>125</v>
-      </c>
-      <c r="D155" s="5">
-        <v>100</v>
-      </c>
-      <c r="E155" s="5">
-        <v>75</v>
-      </c>
-      <c r="F155" s="5">
-        <v>100</v>
-      </c>
-      <c r="H155" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I155" s="5">
-        <v>30</v>
-      </c>
-      <c r="J155" s="5">
-        <v>55</v>
-      </c>
-      <c r="K155" s="5">
-        <v>30</v>
-      </c>
-      <c r="L155" s="5">
-        <v>5</v>
-      </c>
-      <c r="M155" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A156" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B156" s="5">
-        <v>100</v>
-      </c>
-      <c r="C156" s="5">
-        <v>100</v>
-      </c>
-      <c r="D156" s="5">
-        <v>125</v>
-      </c>
-      <c r="E156" s="5">
-        <v>100</v>
-      </c>
-      <c r="F156" s="5">
-        <v>75</v>
-      </c>
-      <c r="H156" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="I156" s="5">
-        <v>30</v>
-      </c>
-      <c r="J156" s="5">
-        <v>30</v>
-      </c>
-      <c r="K156" s="5">
-        <v>55</v>
-      </c>
-      <c r="L156" s="5">
-        <v>30</v>
-      </c>
-      <c r="M156" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A157" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B157" s="5">
-        <v>75</v>
-      </c>
-      <c r="C157" s="5">
-        <v>100</v>
-      </c>
-      <c r="D157" s="5">
-        <v>100</v>
-      </c>
-      <c r="E157" s="5">
-        <v>125</v>
-      </c>
-      <c r="F157" s="5">
-        <v>100</v>
-      </c>
-      <c r="H157" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I157" s="5">
-        <v>5</v>
-      </c>
-      <c r="J157" s="5">
-        <v>30</v>
-      </c>
-      <c r="K157" s="5">
-        <v>30</v>
-      </c>
-      <c r="L157" s="5">
-        <v>55</v>
-      </c>
-      <c r="M157" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
-        <v>118</v>
-      </c>
-      <c r="H159" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A160" t="s">
-        <v>119</v>
-      </c>
-      <c r="H160" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A161" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A163" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A164" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A165" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A166" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A168" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A169" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A170" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A171" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A172" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A174" t="s">
-        <v>154</v>
-      </c>
-      <c r="B174" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A175" t="s">
-        <v>159</v>
-      </c>
-      <c r="B175" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A176" t="s">
-        <v>156</v>
-      </c>
-      <c r="B176" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B177" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>166</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>167</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>174</v>
+        <v>134</v>
+      </c>
+      <c r="B186" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>170</v>
+        <v>139</v>
+      </c>
+      <c r="B187" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>171</v>
+        <v>136</v>
+      </c>
+      <c r="B188" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A189" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A191" t="s">
-        <v>173</v>
+      <c r="B189" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A190" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>197</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A199" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A202" t="s">
-        <v>199</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A201" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A205" t="s">
-        <v>201</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>219</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A211" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A213" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>223</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A225" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -6052,4 +6229,70 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B4D95C-275B-4BAD-BDA9-118F535E1162}">
+  <dimension ref="B2:B12"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B2" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B5" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B7" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B8" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B9" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B10" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B11" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B12" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF2AE69-BAE6-489F-85B8-F8096E598B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7405E34B-6F3A-46DC-8127-5E86CF80EE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="450" windowWidth="19005" windowHeight="14850" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="2340" yWindow="675" windowWidth="26205" windowHeight="14850" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="244">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -2880,10 +2880,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>dps</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・雑魚敵夜限定強化更新　雑魚敵レベルが本来の+3になる　マップに設定のない場合、編成中キャラクターの一番レベルが高いキャラクター+3とする。　出現数が1.5倍になる　ウェーブ数が3になる　大きさが1.5倍になる　雑魚敵の攻撃射程が2倍になる　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　魔女出現時もレベルが同様に高レベルキャラクターの+5，HPは本来の2倍　キャラクターの受けるダメージが2倍になる(各属性防御力、抵抗力に+100のデバフを受ける)　　</t>
   </si>
   <si>
@@ -3048,6 +3044,67 @@
   </si>
   <si>
     <t>フレーム</t>
+  </si>
+  <si>
+    <t>加速度加算が倍で加速度減算が半分</t>
+    <rPh sb="0" eb="3">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンサン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>加速度加算が半分で加速度減算が倍</t>
+    <rPh sb="0" eb="3">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カサン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>カソクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゲンサン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各属性防御</t>
+    <rPh sb="0" eb="3">
+      <t>カクゾクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ボウギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回避率</t>
+    <rPh sb="0" eb="3">
+      <t>カイヒリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -3164,7 +3221,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3183,9 +3240,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3193,6 +3247,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3587,10 +3650,10 @@
         <v>18</v>
       </c>
       <c r="N8" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -3598,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C9" s="5">
         <v>9</v>
@@ -3634,7 +3697,7 @@
         <v>0.5</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O9" s="5">
         <v>0</v>
@@ -3645,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
@@ -3681,7 +3744,7 @@
         <v>0.75</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O10" s="5">
         <v>1</v>
@@ -3692,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C11" s="5">
         <v>8</v>
@@ -3728,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O11" s="5">
         <v>2</v>
@@ -3739,7 +3802,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C12" s="5">
         <v>3</v>
@@ -3775,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O12" s="5">
         <v>3</v>
@@ -3786,7 +3849,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C13" s="5">
         <v>8</v>
@@ -3822,7 +3885,7 @@
         <v>0.5</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O13" s="5">
         <v>2</v>
@@ -3833,7 +3896,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C14" s="5">
         <v>6</v>
@@ -3869,7 +3932,7 @@
         <v>0.75</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O14" s="5">
         <v>3</v>
@@ -3880,7 +3943,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C15" s="5">
         <v>6</v>
@@ -3916,7 +3979,7 @@
         <v>0.75</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O15" s="5">
         <v>0</v>
@@ -3927,7 +3990,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C16" s="5">
         <v>3</v>
@@ -3963,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O16" s="5">
         <v>2</v>
@@ -3974,7 +4037,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C17" s="5">
         <v>1</v>
@@ -4010,61 +4073,60 @@
         <v>1.25</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>10</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C18" s="9">
+      <c r="B18" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="8">
         <v>3</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>333333</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>0</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>99</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>0</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>99</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>0</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="8">
         <v>1000</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="8">
         <v>100</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="8">
         <v>1</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="O18" s="9">
+      <c r="N18" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="O18" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>14</v>
@@ -4103,18 +4165,18 @@
         <v>18</v>
       </c>
       <c r="N20" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="O20" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="O20" s="5" t="s">
-        <v>240</v>
-      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C21" s="5">
         <v>9</v>
@@ -4150,7 +4212,7 @@
         <v>0.5</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O21" s="5">
         <v>0</v>
@@ -4161,7 +4223,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C22" s="5">
         <v>4</v>
@@ -4197,7 +4259,7 @@
         <v>0.75</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O22" s="5">
         <v>1</v>
@@ -4208,7 +4270,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C23" s="5">
         <v>8</v>
@@ -4244,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O23" s="5">
         <v>2</v>
@@ -4255,7 +4317,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="5">
         <v>3</v>
@@ -4291,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O24" s="5">
         <v>3</v>
@@ -4302,7 +4364,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="5">
         <v>8</v>
@@ -4338,7 +4400,7 @@
         <v>0.5</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O25" s="5">
         <v>2</v>
@@ -4349,7 +4411,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="5">
         <v>6</v>
@@ -4385,7 +4447,7 @@
         <v>0.75</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O26" s="5">
         <v>3</v>
@@ -4396,7 +4458,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="5">
         <v>6</v>
@@ -4432,7 +4494,7 @@
         <v>0.75</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O27" s="5">
         <v>0</v>
@@ -4443,7 +4505,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C28" s="5">
         <v>3</v>
@@ -4479,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O28" s="5">
         <v>2</v>
@@ -4490,7 +4552,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="5">
         <v>1</v>
@@ -4526,43 +4588,11 @@
         <v>1.25</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O29" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
@@ -4640,15 +4670,9 @@
       <c r="D50" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
       <c r="H50" s="5" t="s">
         <v>8</v>
       </c>
@@ -4661,7 +4685,14 @@
       <c r="K50" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O50" t="s">
+      <c r="L50" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="N50" s="10"/>
+      <c r="P50" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4676,17 +4707,11 @@
         <v>27</v>
       </c>
       <c r="D51" s="5">
-        <v>9000</v>
-      </c>
-      <c r="E51" s="5">
-        <v>40</v>
-      </c>
-      <c r="F51" s="5">
-        <v>2</v>
-      </c>
-      <c r="G51" s="5">
-        <v>0.4</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
       <c r="H51" s="5">
         <v>15</v>
       </c>
@@ -4699,10 +4724,14 @@
       <c r="K51" s="5">
         <v>1.2</v>
       </c>
+      <c r="L51" s="5">
+        <v>0</v>
+      </c>
       <c r="M51" s="5">
-        <v>3000</v>
-      </c>
-      <c r="O51" t="s">
+        <v>5</v>
+      </c>
+      <c r="N51" s="11"/>
+      <c r="P51" t="s">
         <v>161</v>
       </c>
     </row>
@@ -4717,19 +4746,13 @@
         <v>34</v>
       </c>
       <c r="D52" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E52" s="5">
-        <v>36</v>
-      </c>
-      <c r="F52" s="5">
-        <v>2</v>
-      </c>
-      <c r="G52" s="5">
-        <v>0.5</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
       <c r="H52" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I52" s="5">
         <v>36</v>
@@ -4740,10 +4763,14 @@
       <c r="K52" s="5">
         <v>1.6</v>
       </c>
+      <c r="L52" s="5">
+        <v>10</v>
+      </c>
       <c r="M52" s="5">
-        <v>5000</v>
-      </c>
-      <c r="O52" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="11"/>
+      <c r="P52" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4758,19 +4785,13 @@
         <v>28</v>
       </c>
       <c r="D53" s="5">
-        <v>21000</v>
-      </c>
-      <c r="E53" s="5">
-        <v>32</v>
-      </c>
-      <c r="F53" s="5">
-        <v>2</v>
-      </c>
-      <c r="G53" s="5">
-        <v>0.6</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
       <c r="H53" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I53" s="5">
         <v>90</v>
@@ -4781,10 +4802,14 @@
       <c r="K53" s="5">
         <v>2.2000000000000002</v>
       </c>
+      <c r="L53" s="5">
+        <v>10</v>
+      </c>
       <c r="M53" s="5">
-        <v>7000</v>
-      </c>
-      <c r="O53" t="s">
+        <v>5</v>
+      </c>
+      <c r="N53" s="11"/>
+      <c r="P53" t="s">
         <v>160</v>
       </c>
     </row>
@@ -4799,19 +4824,13 @@
         <v>29</v>
       </c>
       <c r="D54" s="5">
-        <v>27000</v>
-      </c>
-      <c r="E54" s="5">
-        <v>29</v>
-      </c>
-      <c r="F54" s="5">
-        <v>2</v>
-      </c>
-      <c r="G54" s="5">
-        <v>0.7</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
       <c r="H54" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I54" s="5">
         <v>223</v>
@@ -4822,10 +4841,14 @@
       <c r="K54" s="5">
         <v>3</v>
       </c>
+      <c r="L54" s="5">
+        <v>10</v>
+      </c>
       <c r="M54" s="5">
-        <v>9000</v>
-      </c>
-      <c r="O54" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="11"/>
+      <c r="P54" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4842,17 +4865,11 @@
       <c r="D55" s="5">
         <v>33000</v>
       </c>
-      <c r="E55" s="5">
-        <v>26</v>
-      </c>
-      <c r="F55" s="5">
-        <v>2</v>
-      </c>
-      <c r="G55" s="5">
-        <v>0.8</v>
-      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
       <c r="H55" s="5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I55" s="5">
         <v>550</v>
@@ -4863,10 +4880,14 @@
       <c r="K55" s="5">
         <v>4</v>
       </c>
+      <c r="L55" s="5">
+        <v>10</v>
+      </c>
       <c r="M55" s="5">
-        <v>11000</v>
-      </c>
-      <c r="O55" t="s">
+        <v>5</v>
+      </c>
+      <c r="N55" s="11"/>
+      <c r="P55" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4883,17 +4904,11 @@
       <c r="D56" s="5">
         <v>42000</v>
       </c>
-      <c r="E56" s="5">
-        <v>23</v>
-      </c>
-      <c r="F56" s="5">
-        <v>2</v>
-      </c>
-      <c r="G56" s="5">
-        <v>0.9</v>
-      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
       <c r="H56" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I56" s="5">
         <v>1350</v>
@@ -4904,10 +4919,14 @@
       <c r="K56" s="5">
         <v>5.4</v>
       </c>
+      <c r="L56" s="5">
+        <v>10</v>
+      </c>
       <c r="M56" s="5">
-        <v>14000</v>
-      </c>
-      <c r="O56" t="s">
+        <v>5</v>
+      </c>
+      <c r="N56" s="11"/>
+      <c r="P56" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4922,20 +4941,13 @@
         <v>32</v>
       </c>
       <c r="D57" s="5">
-        <f>M57*3</f>
         <v>51000</v>
       </c>
-      <c r="E57" s="5">
-        <v>20</v>
-      </c>
-      <c r="F57" s="5">
-        <v>2</v>
-      </c>
-      <c r="G57" s="5">
-        <v>1</v>
-      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
       <c r="H57" s="5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I57" s="5">
         <v>3300</v>
@@ -4946,9 +4958,13 @@
       <c r="K57" s="5">
         <v>7.2</v>
       </c>
+      <c r="L57" s="5">
+        <v>10</v>
+      </c>
       <c r="M57" s="5">
-        <v>17000</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
@@ -4961,20 +4977,13 @@
         <v>33</v>
       </c>
       <c r="D58" s="5">
-        <f t="shared" ref="D58:D60" si="0">M58*3</f>
         <v>60000</v>
       </c>
-      <c r="E58" s="5">
-        <v>18</v>
-      </c>
-      <c r="F58" s="5">
-        <v>2</v>
-      </c>
-      <c r="G58" s="5">
-        <v>1.2</v>
-      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
       <c r="H58" s="5">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I58" s="5">
         <v>8000</v>
@@ -4983,10 +4992,17 @@
         <v>100</v>
       </c>
       <c r="K58" s="5">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="L58" s="5">
+        <v>10</v>
       </c>
       <c r="M58" s="5">
-        <v>20000</v>
+        <v>5</v>
+      </c>
+      <c r="N58" s="11"/>
+      <c r="P58" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
@@ -5000,20 +5016,13 @@
         <v>193</v>
       </c>
       <c r="D59" s="5">
-        <f t="shared" si="0"/>
-        <v>69000</v>
-      </c>
-      <c r="E59" s="5">
-        <v>16</v>
-      </c>
-      <c r="F59" s="5">
-        <v>2</v>
-      </c>
-      <c r="G59" s="5">
-        <v>1.4</v>
-      </c>
+        <v>80000</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
       <c r="H59" s="5">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I59" s="5">
         <v>12700</v>
@@ -5022,16 +5031,17 @@
         <v>100</v>
       </c>
       <c r="K59" s="5">
-        <v>10.8</v>
+        <v>9</v>
+      </c>
+      <c r="L59" s="5">
+        <v>10</v>
       </c>
       <c r="M59" s="5">
-        <v>23000</v>
-      </c>
-      <c r="O59" t="s">
-        <v>198</v>
-      </c>
-      <c r="P59">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="N59" s="11"/>
+      <c r="P59" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.4">
@@ -5045,37 +5055,30 @@
         <v>194</v>
       </c>
       <c r="D60" s="5">
-        <f t="shared" si="0"/>
-        <v>78000</v>
-      </c>
-      <c r="E60" s="5">
-        <v>14</v>
-      </c>
-      <c r="F60" s="5">
-        <v>2</v>
-      </c>
-      <c r="G60" s="5">
-        <v>1.6</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
       <c r="H60" s="5">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I60" s="5">
-        <v>17400</v>
+        <v>18000</v>
       </c>
       <c r="J60" s="5">
         <v>100</v>
       </c>
       <c r="K60" s="5">
-        <v>12.6</v>
+        <v>10</v>
+      </c>
+      <c r="L60" s="5">
+        <v>10</v>
       </c>
       <c r="M60" s="5">
-        <v>26000</v>
-      </c>
-      <c r="P60">
-        <f>P59*180</f>
-        <v>90000</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
@@ -5088,32 +5091,30 @@
         <v>195</v>
       </c>
       <c r="D61" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E61" s="5">
-        <v>12</v>
-      </c>
-      <c r="F61" s="5">
-        <v>2</v>
-      </c>
-      <c r="G61" s="5">
-        <v>1.8</v>
-      </c>
+        <v>110000</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
       <c r="H61" s="5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I61" s="5">
-        <v>22100</v>
+        <v>20000</v>
       </c>
       <c r="J61" s="5">
         <v>100</v>
       </c>
       <c r="K61" s="5">
-        <v>14.4</v>
+        <v>10.5</v>
+      </c>
+      <c r="L61" s="5">
+        <v>20</v>
       </c>
       <c r="M61" s="5">
-        <v>29000</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N61" s="11"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
@@ -5126,32 +5127,30 @@
         <v>196</v>
       </c>
       <c r="D62" s="5">
-        <v>200000</v>
-      </c>
-      <c r="E62" s="5">
-        <v>10</v>
-      </c>
-      <c r="F62" s="5">
-        <v>2</v>
-      </c>
-      <c r="G62" s="5">
-        <v>2</v>
-      </c>
+        <v>120000</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
       <c r="H62" s="5">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I62" s="5">
-        <v>26800</v>
+        <v>20000</v>
       </c>
       <c r="J62" s="5">
         <v>100</v>
       </c>
       <c r="K62" s="5">
-        <v>16.2</v>
+        <v>11</v>
+      </c>
+      <c r="L62" s="5">
+        <v>20</v>
       </c>
       <c r="M62" s="5">
-        <v>32000</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N62" s="11"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
@@ -5164,32 +5163,30 @@
         <v>197</v>
       </c>
       <c r="D63" s="5">
-        <v>300000</v>
-      </c>
-      <c r="E63" s="5">
-        <v>8</v>
-      </c>
-      <c r="F63" s="5">
-        <v>2</v>
-      </c>
-      <c r="G63" s="5">
-        <v>2.2000000000000002</v>
-      </c>
+        <v>130000</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
       <c r="H63" s="5">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I63" s="5">
-        <v>31500</v>
+        <v>20000</v>
       </c>
       <c r="J63" s="5">
         <v>100</v>
       </c>
       <c r="K63" s="5">
-        <v>18</v>
+        <v>11.5</v>
+      </c>
+      <c r="L63" s="5">
+        <v>20</v>
       </c>
       <c r="M63" s="5">
-        <v>35000</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N63" s="11"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
@@ -5618,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L149" t="str">
         <f>K149&amp;"は、"&amp;K150&amp;"に強く"&amp;K153&amp;"に弱い。"</f>
@@ -5639,7 +5636,7 @@
         <v>255</v>
       </c>
       <c r="K150" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L150" t="str">
         <f>K150&amp;"は、"&amp;K151&amp;"に強く"&amp;K149&amp;"に弱い。"</f>
@@ -5660,10 +5657,10 @@
         <v>107</v>
       </c>
       <c r="K151" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L151" t="str">
-        <f t="shared" ref="L151:L152" si="1">K151&amp;"は、"&amp;K152&amp;"に強く"&amp;K150&amp;"に弱い。"</f>
+        <f t="shared" ref="L151:L152" si="0">K151&amp;"は、"&amp;K152&amp;"に強く"&amp;K150&amp;"に弱い。"</f>
         <v>緑の調和は、黄色の犠牲に強く紫の混沌に弱い。</v>
       </c>
     </row>
@@ -5681,10 +5678,10 @@
         <v>191</v>
       </c>
       <c r="K152" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L152" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>黄色の犠牲は、青い統制に強く緑の調和に弱い。</v>
       </c>
     </row>
@@ -5705,7 +5702,7 @@
         <v>225</v>
       </c>
       <c r="K153" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L153" t="str">
         <f>K153&amp;"は、"&amp;K149&amp;"に強く"&amp;K152&amp;"に弱い。"</f>
@@ -5717,7 +5714,7 @@
         <v>92</v>
       </c>
       <c r="L155" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.4">
@@ -5725,7 +5722,7 @@
         <v>93</v>
       </c>
       <c r="L156" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.4">
@@ -5733,7 +5730,7 @@
         <v>94</v>
       </c>
       <c r="L157" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.4">
@@ -5741,7 +5738,7 @@
         <v>95</v>
       </c>
       <c r="L158" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.4">
@@ -5749,7 +5746,7 @@
         <v>96</v>
       </c>
       <c r="L159" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.4">
@@ -6196,32 +6193,32 @@
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6237,58 +6234,58 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="7" t="s">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="7" t="s">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B5" s="6" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B5" s="7" t="s">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" s="7" t="s">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B7" s="6" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B7" s="7" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B8" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B8" s="7" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B9" s="6" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B9" s="7" t="s">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B10" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B10" s="7" t="s">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B11" s="6" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B11" s="7" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B12" s="6" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B12" s="7" t="s">
-        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/DATA/battle_sys.xlsx
+++ b/public/files/DATA/battle_sys.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7405E34B-6F3A-46DC-8127-5E86CF80EE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6A3302-60E9-4F66-92F2-E5E32EBD549F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="675" windowWidth="26205" windowHeight="14850" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="26205" windowHeight="14850" activeTab="1" xr2:uid="{95876B6F-3B39-4BA7-ADFB-8B03CBB6F143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="6" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="258">
   <si>
     <t>戦闘</t>
     <rPh sb="0" eb="2">
@@ -2995,39 +2995,6 @@
     <t>ゴーレム</t>
   </si>
   <si>
-    <t>ID,名前,出現数,HP,移動速度,移動距離(m),移動間隔(秒),攻撃射程(m),攻撃頻度,攻撃力,重量,デバフ抵抗,大きさ,テクスチャ,フレーム</t>
-  </si>
-  <si>
-    <t>1,スウォーム,9,15,100,6.0,0.5,3.0,0.5,1,5,0,0.5,en003,0</t>
-  </si>
-  <si>
-    <t>2,フライ,4,30,75,4.5,0.45,4.0,0.5,1,10,0,0.75,en003,1</t>
-  </si>
-  <si>
-    <t>3,スピリット,8,50,55,6.0,0.4,4.0,0.5,1,45,50,1.0,en003,2</t>
-  </si>
-  <si>
-    <t>4,マノウォー,3,30,60,6.0,0.3,8.0,1.0,1,15,50,1.0,en003,3</t>
-  </si>
-  <si>
-    <t>5,ゴブリン,8,50,50,3.0,0.25,4.0,1.0,1,35,0,0.5,en001,2</t>
-  </si>
-  <si>
-    <t>6,コボルド,6,90,40,4.5,0.35,4.0,1.0,1,55,50,0.75,en002,3</t>
-  </si>
-  <si>
-    <t>7,オーク,6,90,30,3.9,0.5,8.0,2.0,1,75,0,0.75,en001,0</t>
-  </si>
-  <si>
-    <t>8,オーガ,3,125,25,3.6,0.35,8.0,2.0,1,110,50,1.0,en002,2</t>
-  </si>
-  <si>
-    <t>9,ゴーレム,1,250,25,3.6,0.6,8.0,2.0,1,110,50,1.25,en002,1</t>
-  </si>
-  <si>
-    <t>10,サンドバッグ,3,99999,0,0,99,0,99,0,1000,100,1.0,en001,1</t>
-  </si>
-  <si>
     <t>en003</t>
   </si>
   <si>
@@ -3103,6 +3070,484 @@
     <t>回避率</t>
     <rPh sb="0" eb="3">
       <t>カイヒリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【近接攻撃型】</t>
+    <rPh sb="1" eb="6">
+      <t>キンセツコウゲキガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒼樹，紅華</t>
+    <rPh sb="0" eb="2">
+      <t>アオキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他のキャラクターが1秒以内にレーン移動していたら移動しない</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全メンバーの中で最もHPが低くなると後列に下がる。それ以外の場合前衛に出る</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウレツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の正面に自分の属性の防御力の高い(属性値100未満)キャラクターが来たらレーンを移動する。</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウメン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ミマン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6秒以内に他のメンバーが必殺技を撃っていたら撃たない。</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【後衛型】</t>
+    <rPh sb="1" eb="3">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>李乃果,白蓮</t>
+    <rPh sb="0" eb="3">
+      <t>リノカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハクレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後列から動かない。右端か左端近いほうにレーン移動しようとする。</t>
+    <rPh sb="0" eb="2">
+      <t>コウレツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ミギハシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【支援型】</t>
+    <rPh sb="1" eb="3">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑，黄蘭</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オウラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛に誰かがいれば後列から動かない。前衛がいなくなると前に出ようとする。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウレツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誰も前衛にいないと前衛に出る</t>
+    <rPh sb="0" eb="1">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダムで左右どちらかのレーンを確認し、誰もいないとそちらに移動する。</t>
+    <rPh sb="5" eb="7">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲージがたまれば必殺技を撃つ</t>
+    <rPh sb="8" eb="11">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛にいるとき、目の前に誰かがいたら左右どちらかのレーンへ移動する。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の前列にいるキャラクターが自分の属性の防御力の高い(属性値100未満)キャラクターでなければその正面に移動する。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンレツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ミマン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ショウメン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑魚敵が画面に20匹以上、敵の残り数がまだ半分より多ければ必殺技を撃つ</t>
+    <rPh sb="0" eb="3">
+      <t>ザコテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※雑魚戦</t>
+    <rPh sb="1" eb="4">
+      <t>ザコセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※魔女戦</t>
+    <rPh sb="1" eb="4">
+      <t>マジョセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲージがたまれば撃つ</t>
+    <rPh sb="8" eb="9">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方の2人以上がHPの5%以上を失っていれば撃つ</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウシナ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を撃つときは1/2で後衛中央に向かって移動して撃とうとする。1/2で移動せずそのまま撃つ。</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を撃つときは1/2で後衛中央に向かって移動して撃とうとする。1/2で移動せずそのまま撃つ。</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を撃つときは1/2で前衛中央に向かって移動して撃とうとする。1/2で移動せずそのまま撃つ。</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3111,7 +3556,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3150,12 +3595,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFCCCCCC"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3221,7 +3660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3240,22 +3679,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3650,10 +4077,10 @@
         <v>18</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -3697,7 +4124,7 @@
         <v>0.5</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O9" s="5">
         <v>0</v>
@@ -3744,7 +4171,7 @@
         <v>0.75</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O10" s="5">
         <v>1</v>
@@ -3791,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O11" s="5">
         <v>2</v>
@@ -3838,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O12" s="5">
         <v>3</v>
@@ -3885,7 +4312,7 @@
         <v>0.5</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="O13" s="5">
         <v>2</v>
@@ -3932,7 +4359,7 @@
         <v>0.75</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="O14" s="5">
         <v>3</v>
@@ -3979,7 +4406,7 @@
         <v>0.75</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="O15" s="5">
         <v>0</v>
@@ -4026,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="O16" s="5">
         <v>2</v>
@@ -4073,56 +4500,56 @@
         <v>1.25</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="O17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>10</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="B18" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="7">
         <v>3</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>333333</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>0</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <v>0</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>99</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>0</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>99</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="7">
         <v>0</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="7">
         <v>1000</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="7">
         <v>100</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="7">
         <v>1</v>
       </c>
-      <c r="N18" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="O18" s="8">
+      <c r="N18" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="O18" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4165,14 +4592,14 @@
         <v>18</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -4212,7 +4639,7 @@
         <v>0.5</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O21" s="5">
         <v>0</v>
@@ -4259,7 +4686,7 @@
         <v>0.75</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O22" s="5">
         <v>1</v>
@@ -4306,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O23" s="5">
         <v>2</v>
@@ -4353,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="O24" s="5">
         <v>3</v>
@@ -4400,7 +4827,7 @@
         <v>0.5</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="O25" s="5">
         <v>2</v>
@@ -4447,7 +4874,7 @@
         <v>0.75</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="O26" s="5">
         <v>3</v>
@@ -4494,7 +4921,7 @@
         <v>0.75</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="O27" s="5">
         <v>0</v>
@@ -4541,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="O28" s="5">
         <v>2</v>
@@ -4588,7 +5015,7 @@
         <v>1.25</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="O29" s="5">
         <v>1</v>
@@ -4685,13 +5112,12 @@
       <c r="K50" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L50" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="N50" s="10"/>
+      <c r="L50" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>232</v>
+      </c>
       <c r="P50" t="s">
         <v>157</v>
       </c>
@@ -4730,7 +5156,6 @@
       <c r="M51" s="5">
         <v>5</v>
       </c>
-      <c r="N51" s="11"/>
       <c r="P51" t="s">
         <v>161</v>
       </c>
@@ -4769,7 +5194,6 @@
       <c r="M52" s="5">
         <v>5</v>
       </c>
-      <c r="N52" s="11"/>
       <c r="P52" t="s">
         <v>159</v>
       </c>
@@ -4808,7 +5232,6 @@
       <c r="M53" s="5">
         <v>5</v>
       </c>
-      <c r="N53" s="11"/>
       <c r="P53" t="s">
         <v>160</v>
       </c>
@@ -4847,7 +5270,6 @@
       <c r="M54" s="5">
         <v>5</v>
       </c>
-      <c r="N54" s="11"/>
       <c r="P54" t="s">
         <v>158</v>
       </c>
@@ -4886,7 +5308,6 @@
       <c r="M55" s="5">
         <v>5</v>
       </c>
-      <c r="N55" s="11"/>
       <c r="P55" t="s">
         <v>162</v>
       </c>
@@ -4925,7 +5346,6 @@
       <c r="M56" s="5">
         <v>5</v>
       </c>
-      <c r="N56" s="11"/>
       <c r="P56" t="s">
         <v>163</v>
       </c>
@@ -4964,7 +5384,6 @@
       <c r="M57" s="5">
         <v>5</v>
       </c>
-      <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
@@ -5000,9 +5419,8 @@
       <c r="M58" s="5">
         <v>5</v>
       </c>
-      <c r="N58" s="11"/>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
@@ -5039,9 +5457,8 @@
       <c r="M59" s="5">
         <v>5</v>
       </c>
-      <c r="N59" s="11"/>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.4">
@@ -5078,7 +5495,6 @@
       <c r="M60" s="5">
         <v>5</v>
       </c>
-      <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
@@ -5114,7 +5530,6 @@
       <c r="M61" s="5">
         <v>10</v>
       </c>
-      <c r="N61" s="11"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
@@ -5150,7 +5565,6 @@
       <c r="M62" s="5">
         <v>10</v>
       </c>
-      <c r="N62" s="11"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
@@ -5186,7 +5600,6 @@
       <c r="M63" s="5">
         <v>10</v>
       </c>
-      <c r="N63" s="11"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
@@ -6230,62 +6643,204 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B4D95C-275B-4BAD-BDA9-118F535E1162}">
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B5" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B7" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B8" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B9" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B11" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B12" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
         <v>233</v>
+      </c>
+      <c r="C1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>252</v>
+      </c>
+      <c r="B25" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>251</v>
+      </c>
+      <c r="B37" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>252</v>
+      </c>
+      <c r="B38" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
